--- a/db/A7XLK-1001-TVOC-20210720.xlsx
+++ b/db/A7XLK-1001-TVOC-20210720.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B8F4FF-2AEC-BF49-A0CF-CFA32FF81367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38497270-BE88-FD4C-8966-A99149B9C68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10000" yWindow="520" windowWidth="29360" windowHeight="18360" activeTab="1" xr2:uid="{11F38E42-6FA0-9247-A4F3-693D0F2BA4D6}"/>
+    <workbookView xWindow="4720" yWindow="1420" windowWidth="29360" windowHeight="18360" activeTab="1" xr2:uid="{11F38E42-6FA0-9247-A4F3-693D0F2BA4D6}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Analysis" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="23" r:id="rId3"/>
+    <pivotCache cacheId="25" r:id="rId3"/>
+    <pivotCache cacheId="32" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="198">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -655,6 +656,95 @@
   </si>
   <si>
     <t>平均值 - PM10</t>
+  </si>
+  <si>
+    <t>Category</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文青路</t>
+  </si>
+  <si>
+    <t>樂學路</t>
+  </si>
+  <si>
+    <t>樂學路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樂善二路</t>
+  </si>
+  <si>
+    <t>樂善二路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樟腦寮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZN-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZN-02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZN-03</t>
+  </si>
+  <si>
+    <t>ZN-04</t>
+  </si>
+  <si>
+    <t>ZN-05</t>
+  </si>
+  <si>
+    <t>ZN-06</t>
+  </si>
+  <si>
+    <t>樟腦寮步道</t>
+  </si>
+  <si>
+    <t>樟腦寮步道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>測試點1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>測試點2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>測試點3</t>
+  </si>
+  <si>
+    <t>測試點4</t>
+  </si>
+  <si>
+    <t>測試點5</t>
+  </si>
+  <si>
+    <t>測試點6</t>
+  </si>
+  <si>
+    <t>文化一路</t>
+  </si>
+  <si>
+    <t>華亞二路</t>
+  </si>
+  <si>
+    <t>華亞三路</t>
+  </si>
+  <si>
+    <t>街道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PM2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3597,6 +3687,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="921870271"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -3701,6 +3792,763 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="2400" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>A7 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2400" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>主要道路空氣品質比較</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$C$125</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TVOC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$B$126:$B$132</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>文化一路</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青路</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>華亞二路</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>華亞三路</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>樂善二路</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>樂學路</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>樟腦寮步道</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$C$126:$C$132</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.000_ </c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2.2800000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.1333333333333333E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5900000000000008E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.863636363636364E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.98E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.1857142857142856E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3666666666666666E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-81F2-BF47-A3F4-6E9C0E0AAF76}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="500"/>
+        <c:overlap val="-100"/>
+        <c:axId val="1403173871"/>
+        <c:axId val="941403375"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$D$125</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PM2.5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="l"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$B$126:$B$132</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>文化一路</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青路</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>華亞二路</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>華亞三路</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>樂善二路</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>樂學路</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>樟腦寮步道</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$D$126:$D$132</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.000_ </c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>12.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.333333333333334</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22.285714285714285</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10.833333333333334</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-81F2-BF47-A3F4-6E9C0E0AAF76}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="942196047"/>
+        <c:axId val="942298911"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1403173871"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="楷體-簡" panose="02010600040101010101" pitchFamily="2" charset="-122"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="941403375"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="941403375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>TVOC  </a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.000_ " sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1403173871"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="942298911"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>PM2.5</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.000_ " sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="942196047"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="942196047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="942298911"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3782,6 +4630,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5330,6 +6218,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -5440,13 +6831,49 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="圖表 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6D08357-E4E3-1A41-B714-96B45D983EEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tai-Chung Wang" refreshedDate="44427.814647453706" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="87" xr:uid="{2BC7A732-8AC6-7542-8CDA-A4E87D719B66}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:O88" sheet="工作表1"/>
+    <worksheetSource ref="A1:P88" sheet="Data"/>
   </cacheSource>
   <cacheFields count="15">
     <cacheField name="No" numFmtId="0">
@@ -5714,6 +7141,177 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tai-Chung Wang" refreshedDate="44428.187697800924" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="93" xr:uid="{D3F073CC-3C35-B340-B5F5-1419B365BE8C}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:P94" sheet="Data"/>
+  </cacheSource>
+  <cacheFields count="16">
+    <cacheField name="No" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Street" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems containsBlank="1" count="8">
+        <s v="華亞三路"/>
+        <s v="華亞二路"/>
+        <s v="樂善二路"/>
+        <s v="文化一路"/>
+        <s v="文青路"/>
+        <s v="樂學路"/>
+        <m/>
+        <s v="樟腦寮步道"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Point" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Rank" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="AirIndex" numFmtId="178">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="17"/>
+    </cacheField>
+    <cacheField name="HCHO" numFmtId="176">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6.6000000000000003E-2" count="28">
+        <n v="4.9000000000000002E-2"/>
+        <n v="1.2999999999999999E-2"/>
+        <n v="2.1999999999999999E-2"/>
+        <n v="7.0000000000000001E-3"/>
+        <n v="6.0000000000000001E-3"/>
+        <n v="8.0000000000000002E-3"/>
+        <n v="0.02"/>
+        <n v="1.7999999999999999E-2"/>
+        <n v="5.0000000000000001E-3"/>
+        <n v="4.0000000000000001E-3"/>
+        <n v="8.9999999999999993E-3"/>
+        <n v="1.0999999999999999E-2"/>
+        <n v="2.9000000000000001E-2"/>
+        <n v="1E-3"/>
+        <n v="2E-3"/>
+        <n v="3.0000000000000001E-3"/>
+        <n v="1.4E-2"/>
+        <n v="0.01"/>
+        <n v="2.8000000000000001E-2"/>
+        <n v="2.7E-2"/>
+        <n v="2.5999999999999999E-2"/>
+        <n v="2.3E-2"/>
+        <n v="2.4E-2"/>
+        <n v="0"/>
+        <n v="4.3999999999999997E-2"/>
+        <n v="5.1999999999999998E-2"/>
+        <n v="6.6000000000000003E-2"/>
+        <n v="5.2999999999999999E-2"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="TVOC" numFmtId="176">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="0.28199999999999997" count="43">
+        <n v="0.20699999999999999"/>
+        <n v="0.05"/>
+        <n v="9.4E-2"/>
+        <n v="2.9000000000000001E-2"/>
+        <n v="2.5000000000000001E-2"/>
+        <n v="3.6999999999999998E-2"/>
+        <n v="0.06"/>
+        <n v="8.2000000000000003E-2"/>
+        <n v="7.4999999999999997E-2"/>
+        <n v="5.5E-2"/>
+        <n v="0.02"/>
+        <n v="1.7000000000000001E-2"/>
+        <n v="4.1000000000000002E-2"/>
+        <n v="4.7E-2"/>
+        <n v="0.122"/>
+        <n v="4.0000000000000001E-3"/>
+        <n v="1.6E-2"/>
+        <n v="8.0000000000000002E-3"/>
+        <n v="1.2E-2"/>
+        <n v="5.7000000000000002E-2"/>
+        <n v="3.7999999999999999E-2"/>
+        <n v="0.03"/>
+        <n v="4.2000000000000003E-2"/>
+        <n v="3.3000000000000002E-2"/>
+        <n v="3.4000000000000002E-2"/>
+        <n v="5.2999999999999999E-2"/>
+        <n v="5.8000000000000003E-2"/>
+        <n v="2.1000000000000001E-2"/>
+        <n v="2.4E-2"/>
+        <n v="8.7999999999999995E-2"/>
+        <n v="0.11899999999999999"/>
+        <n v="0.121"/>
+        <n v="0.115"/>
+        <n v="0.114"/>
+        <n v="0.109"/>
+        <n v="9.6000000000000002E-2"/>
+        <n v="0.10199999999999999"/>
+        <n v="7.3999999999999996E-2"/>
+        <n v="0"/>
+        <n v="0.17699999999999999"/>
+        <n v="0.216"/>
+        <n v="0.28199999999999997"/>
+        <n v="0.218"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="PM25" numFmtId="178">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="25" count="21">
+        <n v="6"/>
+        <n v="5"/>
+        <n v="4"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="13"/>
+        <n v="12"/>
+        <n v="10"/>
+        <n v="14"/>
+        <n v="15"/>
+        <n v="16"/>
+        <n v="11"/>
+        <n v="20"/>
+        <n v="21"/>
+        <n v="17"/>
+        <n v="19"/>
+        <n v="22"/>
+        <n v="25"/>
+        <n v="23"/>
+        <n v="18"/>
+        <n v="24"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="PM1" numFmtId="178">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="19"/>
+    </cacheField>
+    <cacheField name="PM10" numFmtId="178">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="29"/>
+    </cacheField>
+    <cacheField name="Temperature" numFmtId="178">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="27" maxValue="35"/>
+    </cacheField>
+    <cacheField name="Humidity" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.49" maxValue="0.8"/>
+    </cacheField>
+    <cacheField name="TVOCS-L1" numFmtId="177">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.16" maxValue="0.16"/>
+    </cacheField>
+    <cacheField name="TVOCS-L2" numFmtId="177">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.3" maxValue="0.3"/>
+    </cacheField>
+    <cacheField name="Date" numFmtId="49">
+      <sharedItems count="3">
+        <s v="2021/07/20"/>
+        <s v="2021/08/19"/>
+        <s v="2021/08/20"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="87">
   <r>
@@ -7198,8 +8796,1890 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="93">
+  <r>
+    <s v="HY3-01"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="柏騰科技"/>
+    <s v="清新"/>
+    <n v="10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="6"/>
+    <n v="30"/>
+    <n v="0.69"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-02"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="新潤翡麗"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="30"/>
+    <n v="0.69"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-03"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="新潤鉑麗"/>
+    <s v="清新"/>
+    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="4"/>
+    <n v="29"/>
+    <n v="0.65"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-04"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="飛捷科技"/>
+    <s v="清新"/>
+    <n v="1"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="4"/>
+    <n v="29"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-05"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="和遠新天地"/>
+    <s v="清新"/>
+    <n v="1"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="4"/>
+    <n v="29"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-06"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="中環三廠"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="29"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-07"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="ASML"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="29"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-08"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="孝思堂"/>
+    <s v="清新"/>
+    <n v="1"/>
+    <x v="6"/>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="4"/>
+    <n v="29"/>
+    <n v="0.68"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-09"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="穩懋A廠"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="7"/>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="30"/>
+    <n v="0.69"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-10"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="穩懋B廠"/>
+    <s v="清新"/>
+    <n v="1"/>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="4"/>
+    <n v="29"/>
+    <n v="0.68"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-11"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="樂活圈1"/>
+    <s v="清新"/>
+    <n v="1"/>
+    <x v="8"/>
+    <x v="10"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="4"/>
+    <n v="30"/>
+    <n v="0.68"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-12"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="樂活圈2"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="9"/>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="29"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY3-13"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="樂活圈3"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="10"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="29"/>
+    <n v="0.7"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-01"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="穩懋B廠"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="10"/>
+    <x v="12"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="6"/>
+    <n v="28"/>
+    <n v="0.71"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-02"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="土地公"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="11"/>
+    <x v="13"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="29"/>
+    <n v="0.66"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-03"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="國際航電"/>
+    <s v="清新"/>
+    <n v="3"/>
+    <x v="12"/>
+    <x v="14"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="6"/>
+    <n v="29"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-04"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="毅嘉科技"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="13"/>
+    <x v="15"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="6"/>
+    <n v="29"/>
+    <n v="0.64"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-05"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="德律科技"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="9"/>
+    <x v="16"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="30"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-06"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="鈺德科技"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="14"/>
+    <x v="17"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="29"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-07"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="神達電腦"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="9"/>
+    <x v="11"/>
+    <x v="3"/>
+    <n v="5"/>
+    <n v="8"/>
+    <n v="29"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-08"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="廣達電腦"/>
+    <s v="清新"/>
+    <n v="3"/>
+    <x v="15"/>
+    <x v="18"/>
+    <x v="4"/>
+    <n v="6"/>
+    <n v="9"/>
+    <n v="28"/>
+    <n v="0.68"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-09"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="亞矽自動"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="14"/>
+    <x v="17"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="6"/>
+    <n v="28"/>
+    <n v="0.7"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-10"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="立德國際"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="9"/>
+    <x v="18"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="6"/>
+    <n v="28"/>
+    <n v="0.71"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-11"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="SGS檢驗"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="13"/>
+    <x v="15"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="28"/>
+    <n v="0.71"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="HY2-01"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="SGS檢驗"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="9"/>
+    <n v="15"/>
+    <n v="30"/>
+    <n v="0.62"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY2-02"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="立德國際"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="4"/>
+    <x v="10"/>
+    <x v="6"/>
+    <n v="9"/>
+    <n v="13"/>
+    <n v="30"/>
+    <n v="0.62"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY2-03"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="亞矽自動"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="16"/>
+    <x v="19"/>
+    <x v="6"/>
+    <n v="9"/>
+    <n v="13"/>
+    <n v="30"/>
+    <n v="0.62"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY2-04"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="廣達電腦"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="10"/>
+    <x v="20"/>
+    <x v="7"/>
+    <n v="7"/>
+    <n v="11"/>
+    <n v="30"/>
+    <n v="0.64"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY2-05"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="神達電腦"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="4"/>
+    <x v="21"/>
+    <x v="8"/>
+    <n v="10"/>
+    <n v="16"/>
+    <n v="30"/>
+    <n v="0.62"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY2-06"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="友達光電"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="17"/>
+    <x v="13"/>
+    <x v="8"/>
+    <n v="10"/>
+    <n v="16"/>
+    <n v="29"/>
+    <n v="0.63"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY2-07"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="鈺德科技"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="17"/>
+    <x v="22"/>
+    <x v="8"/>
+    <n v="10"/>
+    <n v="16"/>
+    <n v="29"/>
+    <n v="0.65"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY2-08"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="毅嘉科技"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="5"/>
+    <x v="23"/>
+    <x v="9"/>
+    <n v="11"/>
+    <n v="17"/>
+    <n v="29"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY2-09"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="國際航電"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="10"/>
+    <n v="12"/>
+    <n v="18"/>
+    <n v="29"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY2-10"/>
+    <s v="華亞二路"/>
+    <x v="1"/>
+    <s v="穩懋B廠P1"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="5"/>
+    <x v="24"/>
+    <x v="8"/>
+    <n v="10"/>
+    <n v="16"/>
+    <n v="29"/>
+    <n v="0.68"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-01"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="穩懋B廠P1"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="17"/>
+    <x v="12"/>
+    <x v="8"/>
+    <n v="10"/>
+    <n v="16"/>
+    <n v="29"/>
+    <n v="0.71"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-02"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="百塑企業"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="1"/>
+    <x v="25"/>
+    <x v="9"/>
+    <n v="11"/>
+    <n v="17"/>
+    <n v="30"/>
+    <n v="0.69"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-03"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="科技六路"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="8"/>
+    <n v="10"/>
+    <n v="16"/>
+    <n v="29"/>
+    <n v="0.65"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-04"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="文化二路252巷"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="6"/>
+    <n v="9"/>
+    <n v="13"/>
+    <n v="30"/>
+    <n v="0.65"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-05"/>
+    <s v="華亞園區"/>
+    <x v="0"/>
+    <s v="有文化"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="8"/>
+    <n v="10"/>
+    <n v="16"/>
+    <n v="30"/>
+    <n v="0.63"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-06"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="中環三廠"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="5"/>
+    <x v="24"/>
+    <x v="5"/>
+    <n v="9"/>
+    <n v="15"/>
+    <n v="32"/>
+    <n v="0.55000000000000004"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-07"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="和遠新天地"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="8"/>
+    <x v="4"/>
+    <x v="9"/>
+    <n v="11"/>
+    <n v="17"/>
+    <n v="32"/>
+    <n v="0.55000000000000004"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-08"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="飛捷科技"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="11"/>
+    <n v="8"/>
+    <n v="12"/>
+    <n v="32"/>
+    <n v="0.56000000000000005"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-09"/>
+    <s v="華亞三路"/>
+    <x v="0"/>
+    <s v="立信螺絲"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="15"/>
+    <x v="18"/>
+    <x v="6"/>
+    <n v="9"/>
+    <n v="13"/>
+    <n v="31"/>
+    <n v="0.56000000000000005"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-10"/>
+    <s v="華亞園區"/>
+    <x v="0"/>
+    <s v="新潤鉑麗"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="15"/>
+    <x v="18"/>
+    <x v="9"/>
+    <n v="11"/>
+    <n v="17"/>
+    <n v="30"/>
+    <n v="0.56000000000000005"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HY3-11"/>
+    <s v="華亞園區"/>
+    <x v="0"/>
+    <s v="新潤翡麗"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="10"/>
+    <x v="23"/>
+    <x v="6"/>
+    <n v="9"/>
+    <n v="13"/>
+    <n v="31"/>
+    <n v="0.56999999999999995"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LS3-01"/>
+    <s v="華亞園區"/>
+    <x v="2"/>
+    <s v="根津苑"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="8"/>
+    <x v="10"/>
+    <x v="8"/>
+    <n v="10"/>
+    <n v="16"/>
+    <n v="30"/>
+    <n v="0.59"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LS3-02"/>
+    <s v="華亞園區"/>
+    <x v="2"/>
+    <s v="華悅城"/>
+    <s v="清新"/>
+    <n v="8"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="12"/>
+    <n v="15"/>
+    <n v="23"/>
+    <n v="30"/>
+    <n v="0.62"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LS2-01"/>
+    <s v="華亞園區"/>
+    <x v="2"/>
+    <s v="金捷市"/>
+    <s v="清新"/>
+    <n v="8"/>
+    <x v="17"/>
+    <x v="12"/>
+    <x v="13"/>
+    <n v="15"/>
+    <n v="24"/>
+    <n v="30"/>
+    <n v="0.64"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WY-01"/>
+    <s v="文化一路"/>
+    <x v="3"/>
+    <s v="123號"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="16"/>
+    <x v="26"/>
+    <x v="5"/>
+    <n v="9"/>
+    <n v="15"/>
+    <n v="30"/>
+    <n v="0.63"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WY-02"/>
+    <s v="文化一路"/>
+    <x v="3"/>
+    <s v="113號"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="8"/>
+    <x v="10"/>
+    <x v="11"/>
+    <n v="8"/>
+    <n v="12"/>
+    <n v="30"/>
+    <n v="0.64"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WY-03"/>
+    <s v="文化一路"/>
+    <x v="3"/>
+    <s v="A7"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="9"/>
+    <x v="16"/>
+    <x v="6"/>
+    <n v="9"/>
+    <n v="13"/>
+    <n v="30"/>
+    <n v="0.65"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WY-04"/>
+    <s v="合宜住宅"/>
+    <x v="3"/>
+    <s v="遠雄新未來"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="14"/>
+    <x v="17"/>
+    <x v="6"/>
+    <n v="9"/>
+    <n v="13"/>
+    <n v="30"/>
+    <n v="0.64"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WY-05"/>
+    <s v="文化一路"/>
+    <x v="3"/>
+    <s v="文青路"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="15"/>
+    <x v="18"/>
+    <x v="9"/>
+    <n v="11"/>
+    <n v="17"/>
+    <n v="30"/>
+    <n v="0.63"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WQ-01"/>
+    <s v="合宜住宅"/>
+    <x v="4"/>
+    <s v="遠雄文青"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="9"/>
+    <x v="16"/>
+    <x v="8"/>
+    <n v="10"/>
+    <n v="16"/>
+    <n v="30"/>
+    <n v="0.65"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WQ-02"/>
+    <s v="合宜住宅"/>
+    <x v="4"/>
+    <s v="名軒快樂家"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="6"/>
+    <n v="9"/>
+    <n v="13"/>
+    <n v="30"/>
+    <n v="0.65"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WQ-03"/>
+    <s v="合宜住宅"/>
+    <x v="4"/>
+    <s v="麗寶快樂家"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="9"/>
+    <x v="16"/>
+    <x v="8"/>
+    <n v="10"/>
+    <n v="16"/>
+    <n v="29"/>
+    <n v="0.69"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WQ-04"/>
+    <s v="合宜住宅"/>
+    <x v="4"/>
+    <s v="水資源中心"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="9"/>
+    <x v="11"/>
+    <x v="9"/>
+    <n v="11"/>
+    <n v="17"/>
+    <n v="32"/>
+    <n v="0.66"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WQ-05"/>
+    <s v="合宜住宅"/>
+    <x v="4"/>
+    <s v="竹城明治"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="10"/>
+    <n v="12"/>
+    <n v="18"/>
+    <n v="30"/>
+    <n v="0.65"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="WQ-06"/>
+    <s v="合宜住宅"/>
+    <x v="4"/>
+    <s v="皇翔歡喜城"/>
+    <s v="清新"/>
+    <n v="8"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="13"/>
+    <n v="15"/>
+    <n v="24"/>
+    <n v="32"/>
+    <n v="0.63"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="NG-01"/>
+    <s v="文青國小"/>
+    <x v="2"/>
+    <s v="富御捷境"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="5"/>
+    <x v="23"/>
+    <x v="14"/>
+    <n v="12"/>
+    <n v="19"/>
+    <n v="33"/>
+    <n v="0.52"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="NG-02"/>
+    <s v="文青國小"/>
+    <x v="2"/>
+    <s v="遠雄新未來2"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="14"/>
+    <n v="12"/>
+    <n v="19"/>
+    <n v="35"/>
+    <n v="0.5"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LS-01"/>
+    <s v="樂善園區"/>
+    <x v="5"/>
+    <s v="皇普MVP"/>
+    <s v="清新"/>
+    <n v="7"/>
+    <x v="8"/>
+    <x v="27"/>
+    <x v="15"/>
+    <n v="14"/>
+    <n v="22"/>
+    <n v="34"/>
+    <n v="0.49"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LS-02"/>
+    <s v="樂善園區"/>
+    <x v="5"/>
+    <s v="耀台北"/>
+    <s v="清新"/>
+    <n v="8"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="13"/>
+    <n v="15"/>
+    <n v="24"/>
+    <n v="34"/>
+    <n v="0.49"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LS-03"/>
+    <s v="樂善園區"/>
+    <x v="5"/>
+    <s v="富宇敦峰"/>
+    <s v="清新"/>
+    <n v="8"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="13"/>
+    <n v="15"/>
+    <n v="24"/>
+    <n v="34"/>
+    <n v="0.52"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LS-04"/>
+    <s v="樂善國小"/>
+    <x v="5"/>
+    <s v="台北國際村"/>
+    <s v="清新"/>
+    <n v="8"/>
+    <x v="15"/>
+    <x v="18"/>
+    <x v="16"/>
+    <n v="16"/>
+    <n v="25"/>
+    <n v="33"/>
+    <n v="0.52"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LS-05"/>
+    <s v="樂善國小"/>
+    <x v="5"/>
+    <s v="鴻典"/>
+    <s v="清新"/>
+    <n v="10"/>
+    <x v="8"/>
+    <x v="28"/>
+    <x v="17"/>
+    <n v="19"/>
+    <n v="29"/>
+    <n v="32"/>
+    <n v="0.54"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LS-06"/>
+    <s v="樂善國小"/>
+    <x v="5"/>
+    <s v="樂捷市"/>
+    <s v="清新"/>
+    <n v="9"/>
+    <x v="8"/>
+    <x v="27"/>
+    <x v="18"/>
+    <n v="17"/>
+    <n v="26"/>
+    <n v="31"/>
+    <n v="0.56000000000000005"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="LS-07"/>
+    <s v="樂善國小"/>
+    <x v="5"/>
+    <s v="奇幻莊園"/>
+    <s v="清新"/>
+    <n v="10"/>
+    <x v="8"/>
+    <x v="27"/>
+    <x v="17"/>
+    <n v="19"/>
+    <n v="29"/>
+    <n v="31"/>
+    <n v="0.56000000000000005"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="HO-01"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="樓梯間"/>
+    <s v="清新"/>
+    <n v="7"/>
+    <x v="2"/>
+    <x v="29"/>
+    <x v="19"/>
+    <n v="13"/>
+    <n v="20"/>
+    <n v="27"/>
+    <n v="0.8"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-02"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="樓梯間"/>
+    <s v="清新"/>
+    <n v="7"/>
+    <x v="12"/>
+    <x v="30"/>
+    <x v="15"/>
+    <n v="14"/>
+    <n v="22"/>
+    <n v="27"/>
+    <n v="0.8"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-03"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="樓梯間"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="18"/>
+    <x v="31"/>
+    <x v="14"/>
+    <n v="12"/>
+    <n v="20"/>
+    <n v="27"/>
+    <n v="0.8"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-04"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="樓梯間"/>
+    <s v="清新"/>
+    <n v="7"/>
+    <x v="18"/>
+    <x v="32"/>
+    <x v="19"/>
+    <n v="13"/>
+    <n v="20"/>
+    <n v="27"/>
+    <n v="0.79"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-05"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="樓梯間"/>
+    <s v="清新"/>
+    <n v="7"/>
+    <x v="19"/>
+    <x v="33"/>
+    <x v="15"/>
+    <n v="14"/>
+    <n v="22"/>
+    <n v="27"/>
+    <n v="0.8"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-06"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="樓梯間"/>
+    <s v="清新"/>
+    <n v="8"/>
+    <x v="20"/>
+    <x v="34"/>
+    <x v="12"/>
+    <n v="15"/>
+    <n v="23"/>
+    <n v="27"/>
+    <n v="0.8"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-07"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="樓梯間"/>
+    <s v="清新"/>
+    <n v="9"/>
+    <x v="21"/>
+    <x v="35"/>
+    <x v="18"/>
+    <n v="17"/>
+    <n v="26"/>
+    <n v="27"/>
+    <n v="0.79"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-08"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="樓梯間"/>
+    <s v="清新"/>
+    <n v="9"/>
+    <x v="6"/>
+    <x v="7"/>
+    <x v="20"/>
+    <n v="18"/>
+    <n v="27"/>
+    <n v="27"/>
+    <n v="0.79"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-09"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="樓梯間"/>
+    <s v="清新"/>
+    <n v="7"/>
+    <x v="22"/>
+    <x v="36"/>
+    <x v="15"/>
+    <n v="14"/>
+    <n v="22"/>
+    <n v="27"/>
+    <n v="0.76"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-10"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="迴廊"/>
+    <s v="清新"/>
+    <n v="6"/>
+    <x v="7"/>
+    <x v="37"/>
+    <x v="14"/>
+    <n v="12"/>
+    <n v="19"/>
+    <n v="27"/>
+    <n v="0.8"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-11"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="迴廊"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="23"/>
+    <x v="38"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="6"/>
+    <n v="27"/>
+    <n v="0.77"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-12"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="迴廊"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="23"/>
+    <x v="38"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="6"/>
+    <n v="27"/>
+    <n v="0.73"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-13"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="迴廊"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="14"/>
+    <x v="17"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="27"/>
+    <n v="0.71"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-14"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="迴廊"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="3"/>
+    <x v="21"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="27"/>
+    <n v="0.71"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-15"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="迴廊"/>
+    <s v="清新"/>
+    <n v="2"/>
+    <x v="9"/>
+    <x v="16"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="5"/>
+    <n v="27"/>
+    <n v="0.69"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-16"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="大廳"/>
+    <s v="清新"/>
+    <n v="8"/>
+    <x v="24"/>
+    <x v="39"/>
+    <x v="7"/>
+    <n v="7"/>
+    <n v="11"/>
+    <n v="27"/>
+    <n v="0.57999999999999996"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-17"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="大廳"/>
+    <s v="清新"/>
+    <n v="11"/>
+    <x v="25"/>
+    <x v="40"/>
+    <x v="7"/>
+    <n v="7"/>
+    <n v="11"/>
+    <n v="27"/>
+    <n v="0.56000000000000005"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-18"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="大廳"/>
+    <s v="清新"/>
+    <n v="17"/>
+    <x v="26"/>
+    <x v="41"/>
+    <x v="7"/>
+    <n v="7"/>
+    <n v="11"/>
+    <n v="27"/>
+    <n v="0.54"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="HO-19"/>
+    <s v="社區內"/>
+    <x v="6"/>
+    <s v="電梯內"/>
+    <s v="清新"/>
+    <n v="12"/>
+    <x v="27"/>
+    <x v="42"/>
+    <x v="10"/>
+    <n v="12"/>
+    <n v="18"/>
+    <n v="29"/>
+    <n v="0.73"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="ZN-01"/>
+    <s v="樟腦寮"/>
+    <x v="7"/>
+    <s v="測試點1"/>
+    <s v="清新"/>
+    <n v="5"/>
+    <x v="15"/>
+    <x v="18"/>
+    <x v="5"/>
+    <n v="9"/>
+    <n v="15"/>
+    <n v="33"/>
+    <n v="0.56999999999999995"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ZN-02"/>
+    <s v="樟腦寮"/>
+    <x v="7"/>
+    <s v="測試點2"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="23"/>
+    <x v="38"/>
+    <x v="7"/>
+    <n v="7"/>
+    <n v="11"/>
+    <n v="32"/>
+    <n v="0.56999999999999995"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ZN-03"/>
+    <s v="樟腦寮"/>
+    <x v="7"/>
+    <s v="測試點3"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="15"/>
+    <x v="18"/>
+    <x v="7"/>
+    <n v="7"/>
+    <n v="11"/>
+    <n v="31"/>
+    <n v="0.61"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ZN-04"/>
+    <s v="樟腦寮"/>
+    <x v="7"/>
+    <s v="測試點4"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="15"/>
+    <x v="18"/>
+    <x v="7"/>
+    <n v="7"/>
+    <n v="11"/>
+    <n v="31"/>
+    <n v="0.65"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ZN-05"/>
+    <s v="樟腦寮"/>
+    <x v="7"/>
+    <s v="測試點5"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="9"/>
+    <x v="11"/>
+    <x v="7"/>
+    <n v="7"/>
+    <n v="11"/>
+    <n v="30"/>
+    <n v="0.66"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ZN-06"/>
+    <s v="樟腦寮"/>
+    <x v="7"/>
+    <s v="測試點6"/>
+    <s v="清新"/>
+    <n v="4"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="6"/>
+    <n v="9"/>
+    <n v="13"/>
+    <n v="30"/>
+    <n v="0.67"/>
+    <n v="0.16"/>
+    <n v="0.3"/>
+    <x v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{720ED964-7BC8-684A-BBAE-C23D41EA4814}" name="樞紐分析表3" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37ED737D-3F36-E24F-9BD7-02891A5A600F}" name="樞紐分析表4" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B114:D122" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0">
+      <items count="29">
+        <item x="23"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="24"/>
+        <item x="0"/>
+        <item x="25"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="176" showAll="0">
+      <items count="44">
+        <item x="38"/>
+        <item x="15"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="21"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="5"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="22"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="19"/>
+        <item x="26"/>
+        <item x="6"/>
+        <item x="37"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="29"/>
+        <item x="2"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="34"/>
+        <item x="33"/>
+        <item x="32"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="14"/>
+        <item x="39"/>
+        <item x="0"/>
+        <item x="40"/>
+        <item x="42"/>
+        <item x="41"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="178" showAll="0">
+      <items count="22">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="14"/>
+        <item x="19"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="20"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="15" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="平均值 - TVOC" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="176"/>
+    <dataField name="平均值 - PM25" fld="8" subtotal="average" baseField="0" baseItem="0" numFmtId="176"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{720ED964-7BC8-684A-BBAE-C23D41EA4814}" name="樞紐分析表3" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="B77:E82" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -7426,8 +10906,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6D587E1-3F11-8949-B3A1-51B0FE88E26C}" name="樞紐分析表2" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6D587E1-3F11-8949-B3A1-51B0FE88E26C}" name="樞紐分析表2" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="B46:G51" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -7773,8 +11253,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55D91BA8-991E-C349-8944-9ABD03A461D9}" name="樞紐分析表1" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55D91BA8-991E-C349-8944-9ABD03A461D9}" name="樞紐分析表1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="B7:E13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -8196,18 +11676,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F155B05C-8FBC-5D47-8E46-498532CDE74B}">
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:P94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="10.83203125" style="5"/>
-    <col min="6" max="7" width="10.83203125" style="1"/>
-    <col min="8" max="11" width="10.83203125" style="5"/>
-    <col min="12" max="12" width="10.83203125" style="2"/>
-    <col min="13" max="14" width="10.83203125" style="3"/>
-    <col min="15" max="15" width="10.83203125" style="4"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="5"/>
+    <col min="7" max="8" width="10.83203125" style="1"/>
+    <col min="9" max="12" width="10.83203125" style="5"/>
+    <col min="13" max="13" width="10.83203125" style="2"/>
+    <col min="14" max="15" width="10.83203125" style="3"/>
+    <col min="16" max="16" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8215,46 +11696,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -8262,46 +11746,49 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F2" s="5">
         <v>10</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>0.20699999999999999</v>
       </c>
-      <c r="H2" s="5">
+      <c r="I2" s="5">
         <v>6</v>
       </c>
-      <c r="I2" s="5">
+      <c r="J2" s="5">
         <v>4</v>
       </c>
-      <c r="J2" s="5">
+      <c r="K2" s="5">
         <v>6</v>
       </c>
-      <c r="K2" s="5">
+      <c r="L2" s="5">
         <v>30</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="2">
         <v>0.69</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="3">
         <v>0.16</v>
       </c>
-      <c r="N2" s="3">
+      <c r="O2" s="3">
         <v>0.3</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -8309,46 +11796,49 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="5">
         <v>2</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>0.05</v>
       </c>
-      <c r="H3" s="5">
+      <c r="I3" s="5">
         <v>5</v>
       </c>
-      <c r="I3" s="5">
+      <c r="J3" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
+      <c r="K3" s="5">
         <v>5</v>
       </c>
-      <c r="K3" s="5">
+      <c r="L3" s="5">
         <v>30</v>
       </c>
-      <c r="L3" s="2">
+      <c r="M3" s="2">
         <v>0.69</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="3">
         <v>0.16</v>
       </c>
-      <c r="N3" s="3">
+      <c r="O3" s="3">
         <v>0.3</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -8356,46 +11846,49 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F4" s="5">
         <v>1</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>9.4E-2</v>
       </c>
-      <c r="H4" s="5">
+      <c r="I4" s="5">
         <v>4</v>
       </c>
-      <c r="I4" s="5">
+      <c r="J4" s="5">
         <v>3</v>
       </c>
-      <c r="J4" s="5">
+      <c r="K4" s="5">
         <v>4</v>
       </c>
-      <c r="K4" s="5">
+      <c r="L4" s="5">
         <v>29</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2">
         <v>0.65</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>0.16</v>
       </c>
-      <c r="N4" s="3">
+      <c r="O4" s="3">
         <v>0.3</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -8403,46 +11896,49 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5" s="5">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="H5" s="5">
+      <c r="I5" s="5">
         <v>4</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="5">
         <v>3</v>
       </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
         <v>4</v>
       </c>
-      <c r="K5" s="5">
+      <c r="L5" s="5">
         <v>29</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2">
         <v>0.67</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>0.16</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="3">
         <v>0.3</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="P5" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -8450,46 +11946,49 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="5">
+      <c r="F6" s="5">
         <v>1</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H6" s="5">
+      <c r="I6" s="5">
         <v>4</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>3</v>
       </c>
-      <c r="J6" s="5">
+      <c r="K6" s="5">
         <v>4</v>
       </c>
-      <c r="K6" s="5">
+      <c r="L6" s="5">
         <v>29</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
         <v>0.67</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>0.16</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>0.3</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -8497,46 +11996,49 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="5">
+      <c r="F7" s="5">
         <v>2</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="H7" s="5">
+      <c r="I7" s="5">
         <v>5</v>
       </c>
-      <c r="I7" s="5">
+      <c r="J7" s="5">
         <v>3</v>
       </c>
-      <c r="J7" s="5">
+      <c r="K7" s="5">
         <v>5</v>
       </c>
-      <c r="K7" s="5">
+      <c r="L7" s="5">
         <v>29</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>0.67</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>0.16</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="3">
         <v>0.3</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -8544,46 +12046,49 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
         <v>33</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="5">
+      <c r="F8" s="5">
         <v>2</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>0.06</v>
       </c>
-      <c r="H8" s="5">
+      <c r="I8" s="5">
         <v>5</v>
       </c>
-      <c r="I8" s="5">
+      <c r="J8" s="5">
         <v>3</v>
       </c>
-      <c r="J8" s="5">
+      <c r="K8" s="5">
         <v>5</v>
       </c>
-      <c r="K8" s="5">
+      <c r="L8" s="5">
         <v>29</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
         <v>0.67</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>0.16</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>0.3</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="P8" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -8591,46 +12096,49 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="5">
+      <c r="F9" s="5">
         <v>1</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>0.02</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="H9" s="5">
+      <c r="I9" s="5">
         <v>4</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="5">
         <v>3</v>
       </c>
-      <c r="J9" s="5">
+      <c r="K9" s="5">
         <v>4</v>
       </c>
-      <c r="K9" s="5">
+      <c r="L9" s="5">
         <v>29</v>
       </c>
-      <c r="L9" s="2">
+      <c r="M9" s="2">
         <v>0.68</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>0.16</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>0.3</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="P9" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -8638,46 +12146,49 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
         <v>35</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="5">
+      <c r="F10" s="5">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="H10" s="5">
+      <c r="I10" s="5">
         <v>5</v>
       </c>
-      <c r="I10" s="5">
+      <c r="J10" s="5">
         <v>3</v>
       </c>
-      <c r="J10" s="5">
+      <c r="K10" s="5">
         <v>5</v>
       </c>
-      <c r="K10" s="5">
+      <c r="L10" s="5">
         <v>30</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
         <v>0.69</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>0.16</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>0.3</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="P10" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8685,46 +12196,49 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="5">
+      <c r="F11" s="5">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>5.5E-2</v>
       </c>
-      <c r="H11" s="5">
+      <c r="I11" s="5">
         <v>4</v>
       </c>
-      <c r="I11" s="5">
+      <c r="J11" s="5">
         <v>3</v>
       </c>
-      <c r="J11" s="5">
+      <c r="K11" s="5">
         <v>4</v>
       </c>
-      <c r="K11" s="5">
+      <c r="L11" s="5">
         <v>29</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
         <v>0.68</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>0.16</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="3">
         <v>0.3</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="P11" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8732,46 +12246,49 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
         <v>37</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="5">
+      <c r="F12" s="5">
         <v>1</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>0.02</v>
       </c>
-      <c r="H12" s="5">
+      <c r="I12" s="5">
         <v>4</v>
       </c>
-      <c r="I12" s="5">
+      <c r="J12" s="5">
         <v>3</v>
       </c>
-      <c r="J12" s="5">
+      <c r="K12" s="5">
         <v>4</v>
       </c>
-      <c r="K12" s="5">
+      <c r="L12" s="5">
         <v>30</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <v>0.68</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>0.16</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>0.3</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="P12" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -8779,46 +12296,49 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="5">
+      <c r="F13" s="5">
         <v>2</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="H13" s="5">
+      <c r="I13" s="5">
         <v>5</v>
       </c>
-      <c r="I13" s="5">
+      <c r="J13" s="5">
         <v>3</v>
       </c>
-      <c r="J13" s="5">
+      <c r="K13" s="5">
         <v>5</v>
       </c>
-      <c r="K13" s="5">
+      <c r="L13" s="5">
         <v>29</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M13" s="2">
         <v>0.67</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>0.16</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="3">
         <v>0.3</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="P13" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -8826,46 +12346,49 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
         <v>39</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="5">
+      <c r="F14" s="5">
         <v>2</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="H14" s="5">
+      <c r="I14" s="5">
         <v>5</v>
       </c>
-      <c r="I14" s="5">
+      <c r="J14" s="5">
         <v>3</v>
       </c>
-      <c r="J14" s="5">
+      <c r="K14" s="5">
         <v>5</v>
       </c>
-      <c r="K14" s="5">
+      <c r="L14" s="5">
         <v>29</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="2">
         <v>0.7</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>0.16</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>0.3</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="P14" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -8873,46 +12396,49 @@
         <v>40</v>
       </c>
       <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
         <v>36</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="5">
+      <c r="F15" s="5">
         <v>2</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="H15" s="5">
+      <c r="I15" s="5">
         <v>6</v>
       </c>
-      <c r="I15" s="5">
+      <c r="J15" s="5">
         <v>4</v>
       </c>
-      <c r="J15" s="5">
+      <c r="K15" s="5">
         <v>6</v>
       </c>
-      <c r="K15" s="5">
+      <c r="L15" s="5">
         <v>28</v>
       </c>
-      <c r="L15" s="2">
+      <c r="M15" s="2">
         <v>0.71</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>0.16</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>0.3</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="P15" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -8920,46 +12446,49 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
         <v>49</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="5">
+      <c r="F16" s="5">
         <v>2</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>4.7E-2</v>
       </c>
-      <c r="H16" s="5">
+      <c r="I16" s="5">
         <v>5</v>
       </c>
-      <c r="I16" s="5">
+      <c r="J16" s="5">
         <v>3</v>
       </c>
-      <c r="J16" s="5">
+      <c r="K16" s="5">
         <v>5</v>
       </c>
-      <c r="K16" s="5">
+      <c r="L16" s="5">
         <v>29</v>
       </c>
-      <c r="L16" s="2">
+      <c r="M16" s="2">
         <v>0.66</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>0.16</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>0.3</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="P16" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -8967,46 +12496,49 @@
         <v>40</v>
       </c>
       <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
         <v>50</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="5">
+      <c r="F17" s="5">
         <v>3</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>0.122</v>
       </c>
-      <c r="H17" s="5">
+      <c r="I17" s="5">
         <v>6</v>
       </c>
-      <c r="I17" s="5">
+      <c r="J17" s="5">
         <v>4</v>
       </c>
-      <c r="J17" s="5">
+      <c r="K17" s="5">
         <v>6</v>
       </c>
-      <c r="K17" s="5">
+      <c r="L17" s="5">
         <v>29</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="2">
         <v>0.67</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>0.16</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>0.3</v>
       </c>
-      <c r="O17" s="4" t="s">
+      <c r="P17" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -9014,46 +12546,49 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
         <v>51</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="5">
+      <c r="F18" s="5">
         <v>2</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
         <v>1E-3</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="H18" s="5">
+      <c r="I18" s="5">
         <v>6</v>
       </c>
-      <c r="I18" s="5">
+      <c r="J18" s="5">
         <v>4</v>
       </c>
-      <c r="J18" s="5">
+      <c r="K18" s="5">
         <v>6</v>
       </c>
-      <c r="K18" s="5">
+      <c r="L18" s="5">
         <v>29</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
         <v>0.64</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>0.16</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>0.3</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="P18" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -9061,46 +12596,49 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
         <v>52</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="5">
+      <c r="F19" s="5">
         <v>2</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="H19" s="5">
+      <c r="I19" s="5">
         <v>5</v>
       </c>
-      <c r="I19" s="5">
+      <c r="J19" s="5">
         <v>3</v>
       </c>
-      <c r="J19" s="5">
+      <c r="K19" s="5">
         <v>5</v>
       </c>
-      <c r="K19" s="5">
+      <c r="L19" s="5">
         <v>30</v>
       </c>
-      <c r="L19" s="2">
+      <c r="M19" s="2">
         <v>0.67</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>0.16</v>
       </c>
-      <c r="N19" s="3">
+      <c r="O19" s="3">
         <v>0.3</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="P19" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -9108,46 +12646,49 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" t="s">
         <v>53</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="5">
+      <c r="F20" s="5">
         <v>2</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
         <v>2E-3</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="H20" s="5">
+      <c r="I20" s="5">
         <v>5</v>
       </c>
-      <c r="I20" s="5">
+      <c r="J20" s="5">
         <v>3</v>
       </c>
-      <c r="J20" s="5">
+      <c r="K20" s="5">
         <v>5</v>
       </c>
-      <c r="K20" s="5">
+      <c r="L20" s="5">
         <v>29</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="2">
         <v>0.67</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>0.16</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>0.3</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="P20" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -9155,46 +12696,49 @@
         <v>40</v>
       </c>
       <c r="C21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" t="s">
         <v>54</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="5">
+      <c r="F21" s="5">
         <v>2</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="H21" s="5">
+      <c r="I21" s="5">
         <v>7</v>
       </c>
-      <c r="I21" s="5">
+      <c r="J21" s="5">
         <v>5</v>
       </c>
-      <c r="J21" s="5">
+      <c r="K21" s="5">
         <v>8</v>
       </c>
-      <c r="K21" s="5">
+      <c r="L21" s="5">
         <v>29</v>
       </c>
-      <c r="L21" s="2">
+      <c r="M21" s="2">
         <v>0.67</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>0.16</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>0.3</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="P21" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -9202,46 +12746,49 @@
         <v>40</v>
       </c>
       <c r="C22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" t="s">
         <v>58</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="5">
+      <c r="F22" s="5">
         <v>3</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="H22" s="5">
+      <c r="I22" s="5">
         <v>8</v>
       </c>
-      <c r="I22" s="5">
+      <c r="J22" s="5">
         <v>6</v>
       </c>
-      <c r="J22" s="5">
+      <c r="K22" s="5">
         <v>9</v>
       </c>
-      <c r="K22" s="5">
+      <c r="L22" s="5">
         <v>28</v>
       </c>
-      <c r="L22" s="2">
+      <c r="M22" s="2">
         <v>0.68</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>0.16</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>0.3</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="P22" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -9249,46 +12796,49 @@
         <v>40</v>
       </c>
       <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
         <v>59</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="5">
+      <c r="F23" s="5">
         <v>2</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>2E-3</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="H23" s="5">
+      <c r="I23" s="5">
         <v>6</v>
       </c>
-      <c r="I23" s="5">
+      <c r="J23" s="5">
         <v>4</v>
       </c>
-      <c r="J23" s="5">
+      <c r="K23" s="5">
         <v>6</v>
       </c>
-      <c r="K23" s="5">
+      <c r="L23" s="5">
         <v>28</v>
       </c>
-      <c r="L23" s="2">
+      <c r="M23" s="2">
         <v>0.7</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>0.16</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>0.3</v>
       </c>
-      <c r="O23" s="4" t="s">
+      <c r="P23" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -9296,46 +12846,49 @@
         <v>40</v>
       </c>
       <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" t="s">
         <v>60</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="5">
+      <c r="F24" s="5">
         <v>2</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="H24" s="5">
+      <c r="I24" s="5">
         <v>6</v>
       </c>
-      <c r="I24" s="5">
+      <c r="J24" s="5">
         <v>4</v>
       </c>
-      <c r="J24" s="5">
+      <c r="K24" s="5">
         <v>6</v>
       </c>
-      <c r="K24" s="5">
+      <c r="L24" s="5">
         <v>28</v>
       </c>
-      <c r="L24" s="2">
+      <c r="M24" s="2">
         <v>0.71</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>0.16</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>0.3</v>
       </c>
-      <c r="O24" s="4" t="s">
+      <c r="P24" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -9343,46 +12896,49 @@
         <v>40</v>
       </c>
       <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
         <v>61</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="5">
+      <c r="F25" s="5">
         <v>2</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
         <v>1E-3</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="H25" s="5">
+      <c r="I25" s="5">
         <v>5</v>
       </c>
-      <c r="I25" s="5">
+      <c r="J25" s="5">
         <v>3</v>
       </c>
-      <c r="J25" s="5">
+      <c r="K25" s="5">
         <v>5</v>
       </c>
-      <c r="K25" s="5">
+      <c r="L25" s="5">
         <v>28</v>
       </c>
-      <c r="L25" s="2">
+      <c r="M25" s="2">
         <v>0.71</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N25" s="3">
         <v>0.16</v>
       </c>
-      <c r="N25" s="3">
+      <c r="O25" s="3">
         <v>0.3</v>
       </c>
-      <c r="O25" s="4" t="s">
+      <c r="P25" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -9390,46 +12946,49 @@
         <v>40</v>
       </c>
       <c r="C26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" t="s">
         <v>61</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="5">
+      <c r="F26" s="5">
         <v>5</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="H26" s="5">
+      <c r="I26" s="5">
         <v>13</v>
       </c>
-      <c r="I26" s="5">
+      <c r="J26" s="5">
         <v>9</v>
       </c>
-      <c r="J26" s="5">
+      <c r="K26" s="5">
         <v>15</v>
       </c>
-      <c r="K26" s="5">
+      <c r="L26" s="5">
         <v>30</v>
       </c>
-      <c r="L26" s="2">
+      <c r="M26" s="2">
         <v>0.62</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>0.16</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>0.3</v>
       </c>
-      <c r="O26" s="4" t="s">
+      <c r="P26" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -9437,46 +12996,49 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
         <v>60</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="5">
+      <c r="F27" s="5">
         <v>4</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G27" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <v>0.02</v>
       </c>
-      <c r="H27" s="5">
+      <c r="I27" s="5">
         <v>12</v>
       </c>
-      <c r="I27" s="5">
+      <c r="J27" s="5">
         <v>9</v>
       </c>
-      <c r="J27" s="5">
+      <c r="K27" s="5">
         <v>13</v>
       </c>
-      <c r="K27" s="5">
+      <c r="L27" s="5">
         <v>30</v>
       </c>
-      <c r="L27" s="2">
+      <c r="M27" s="2">
         <v>0.62</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>0.16</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>0.3</v>
       </c>
-      <c r="O27" s="4" t="s">
+      <c r="P27" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -9484,46 +13046,49 @@
         <v>40</v>
       </c>
       <c r="C28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" t="s">
         <v>59</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="5">
+      <c r="F28" s="5">
         <v>4</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
         <v>1.4E-2</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="H28" s="5">
+      <c r="I28" s="5">
         <v>12</v>
       </c>
-      <c r="I28" s="5">
+      <c r="J28" s="5">
         <v>9</v>
       </c>
-      <c r="J28" s="5">
+      <c r="K28" s="5">
         <v>13</v>
       </c>
-      <c r="K28" s="5">
+      <c r="L28" s="5">
         <v>30</v>
       </c>
-      <c r="L28" s="2">
+      <c r="M28" s="2">
         <v>0.62</v>
       </c>
-      <c r="M28" s="3">
+      <c r="N28" s="3">
         <v>0.16</v>
       </c>
-      <c r="N28" s="3">
+      <c r="O28" s="3">
         <v>0.3</v>
       </c>
-      <c r="O28" s="4" t="s">
+      <c r="P28" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -9531,46 +13096,49 @@
         <v>40</v>
       </c>
       <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" t="s">
         <v>58</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="5">
+      <c r="F29" s="5">
         <v>4</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="H29" s="5">
+      <c r="I29" s="5">
         <v>10</v>
       </c>
-      <c r="I29" s="5">
+      <c r="J29" s="5">
         <v>7</v>
       </c>
-      <c r="J29" s="5">
+      <c r="K29" s="5">
         <v>11</v>
       </c>
-      <c r="K29" s="5">
+      <c r="L29" s="5">
         <v>30</v>
       </c>
-      <c r="L29" s="2">
+      <c r="M29" s="2">
         <v>0.64</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>0.16</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>0.3</v>
       </c>
-      <c r="O29" s="4" t="s">
+      <c r="P29" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>45</v>
       </c>
@@ -9578,46 +13146,49 @@
         <v>40</v>
       </c>
       <c r="C30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" t="s">
         <v>54</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="5">
+      <c r="F30" s="5">
         <v>5</v>
       </c>
-      <c r="F30" s="1">
+      <c r="G30" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <v>0.03</v>
       </c>
-      <c r="H30" s="5">
+      <c r="I30" s="5">
         <v>14</v>
       </c>
-      <c r="I30" s="5">
+      <c r="J30" s="5">
         <v>10</v>
       </c>
-      <c r="J30" s="5">
+      <c r="K30" s="5">
         <v>16</v>
       </c>
-      <c r="K30" s="5">
+      <c r="L30" s="5">
         <v>30</v>
       </c>
-      <c r="L30" s="2">
+      <c r="M30" s="2">
         <v>0.62</v>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="3">
         <v>0.16</v>
       </c>
-      <c r="N30" s="3">
+      <c r="O30" s="3">
         <v>0.3</v>
       </c>
-      <c r="O30" s="4" t="s">
+      <c r="P30" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -9625,46 +13196,49 @@
         <v>40</v>
       </c>
       <c r="C31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" t="s">
         <v>67</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>15</v>
       </c>
-      <c r="E31" s="5">
+      <c r="F31" s="5">
         <v>5</v>
       </c>
-      <c r="F31" s="1">
+      <c r="G31" s="1">
         <v>0.01</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <v>4.7E-2</v>
       </c>
-      <c r="H31" s="5">
+      <c r="I31" s="5">
         <v>14</v>
       </c>
-      <c r="I31" s="5">
+      <c r="J31" s="5">
         <v>10</v>
       </c>
-      <c r="J31" s="5">
+      <c r="K31" s="5">
         <v>16</v>
       </c>
-      <c r="K31" s="5">
+      <c r="L31" s="5">
         <v>29</v>
       </c>
-      <c r="L31" s="2">
+      <c r="M31" s="2">
         <v>0.63</v>
       </c>
-      <c r="M31" s="3">
+      <c r="N31" s="3">
         <v>0.16</v>
       </c>
-      <c r="N31" s="3">
+      <c r="O31" s="3">
         <v>0.3</v>
       </c>
-      <c r="O31" s="4" t="s">
+      <c r="P31" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -9672,46 +13246,49 @@
         <v>40</v>
       </c>
       <c r="C32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" t="s">
         <v>53</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="5">
+      <c r="F32" s="5">
         <v>5</v>
       </c>
-      <c r="F32" s="1">
+      <c r="G32" s="1">
         <v>0.01</v>
       </c>
-      <c r="G32" s="1">
+      <c r="H32" s="1">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="H32" s="5">
+      <c r="I32" s="5">
         <v>14</v>
       </c>
-      <c r="I32" s="5">
+      <c r="J32" s="5">
         <v>10</v>
       </c>
-      <c r="J32" s="5">
+      <c r="K32" s="5">
         <v>16</v>
       </c>
-      <c r="K32" s="5">
+      <c r="L32" s="5">
         <v>29</v>
       </c>
-      <c r="L32" s="2">
+      <c r="M32" s="2">
         <v>0.65</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>0.16</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>0.3</v>
       </c>
-      <c r="O32" s="4" t="s">
+      <c r="P32" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>48</v>
       </c>
@@ -9719,46 +13296,49 @@
         <v>40</v>
       </c>
       <c r="C33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" t="s">
         <v>51</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="5">
+      <c r="F33" s="5">
         <v>6</v>
       </c>
-      <c r="F33" s="1">
+      <c r="G33" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="H33" s="5">
+      <c r="I33" s="5">
         <v>15</v>
       </c>
-      <c r="I33" s="5">
+      <c r="J33" s="5">
         <v>11</v>
       </c>
-      <c r="J33" s="5">
+      <c r="K33" s="5">
         <v>17</v>
       </c>
-      <c r="K33" s="5">
+      <c r="L33" s="5">
         <v>29</v>
       </c>
-      <c r="L33" s="2">
+      <c r="M33" s="2">
         <v>0.67</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>0.16</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>0.3</v>
       </c>
-      <c r="O33" s="4" t="s">
+      <c r="P33" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -9766,46 +13346,49 @@
         <v>40</v>
       </c>
       <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" t="s">
         <v>50</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>15</v>
       </c>
-      <c r="E34" s="5">
+      <c r="F34" s="5">
         <v>6</v>
       </c>
-      <c r="F34" s="1">
+      <c r="G34" s="1">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="H34" s="5">
+      <c r="I34" s="5">
         <v>16</v>
       </c>
-      <c r="I34" s="5">
+      <c r="J34" s="5">
         <v>12</v>
       </c>
-      <c r="J34" s="5">
+      <c r="K34" s="5">
         <v>18</v>
       </c>
-      <c r="K34" s="5">
+      <c r="L34" s="5">
         <v>29</v>
       </c>
-      <c r="L34" s="2">
+      <c r="M34" s="2">
         <v>0.67</v>
       </c>
-      <c r="M34" s="3">
+      <c r="N34" s="3">
         <v>0.16</v>
       </c>
-      <c r="N34" s="3">
+      <c r="O34" s="3">
         <v>0.3</v>
       </c>
-      <c r="O34" s="4" t="s">
+      <c r="P34" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -9813,46 +13396,49 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" t="s">
         <v>68</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="5">
+      <c r="F35" s="5">
         <v>5</v>
       </c>
-      <c r="F35" s="1">
+      <c r="G35" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G35" s="1">
+      <c r="H35" s="1">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="H35" s="5">
+      <c r="I35" s="5">
         <v>14</v>
       </c>
-      <c r="I35" s="5">
+      <c r="J35" s="5">
         <v>10</v>
       </c>
-      <c r="J35" s="5">
+      <c r="K35" s="5">
         <v>16</v>
       </c>
-      <c r="K35" s="5">
+      <c r="L35" s="5">
         <v>29</v>
       </c>
-      <c r="L35" s="2">
+      <c r="M35" s="2">
         <v>0.68</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>0.16</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>0.3</v>
       </c>
-      <c r="O35" s="4" t="s">
+      <c r="P35" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -9860,46 +13446,49 @@
         <v>12</v>
       </c>
       <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
         <v>68</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="5">
+      <c r="F36" s="5">
         <v>5</v>
       </c>
-      <c r="F36" s="1">
+      <c r="G36" s="1">
         <v>0.01</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="1">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="H36" s="5">
+      <c r="I36" s="5">
         <v>14</v>
       </c>
-      <c r="I36" s="5">
+      <c r="J36" s="5">
         <v>10</v>
       </c>
-      <c r="J36" s="5">
+      <c r="K36" s="5">
         <v>16</v>
       </c>
-      <c r="K36" s="5">
+      <c r="L36" s="5">
         <v>29</v>
       </c>
-      <c r="L36" s="2">
+      <c r="M36" s="2">
         <v>0.71</v>
       </c>
-      <c r="M36" s="3">
+      <c r="N36" s="3">
         <v>0.16</v>
       </c>
-      <c r="N36" s="3">
+      <c r="O36" s="3">
         <v>0.3</v>
       </c>
-      <c r="O36" s="4" t="s">
+      <c r="P36" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -9907,46 +13496,49 @@
         <v>12</v>
       </c>
       <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
         <v>69</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="5">
+      <c r="F37" s="5">
         <v>6</v>
       </c>
-      <c r="F37" s="1">
+      <c r="G37" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="G37" s="1">
+      <c r="H37" s="1">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="H37" s="5">
+      <c r="I37" s="5">
         <v>15</v>
       </c>
-      <c r="I37" s="5">
+      <c r="J37" s="5">
         <v>11</v>
       </c>
-      <c r="J37" s="5">
+      <c r="K37" s="5">
         <v>17</v>
       </c>
-      <c r="K37" s="5">
+      <c r="L37" s="5">
         <v>30</v>
       </c>
-      <c r="L37" s="2">
+      <c r="M37" s="2">
         <v>0.69</v>
       </c>
-      <c r="M37" s="3">
+      <c r="N37" s="3">
         <v>0.16</v>
       </c>
-      <c r="N37" s="3">
+      <c r="O37" s="3">
         <v>0.3</v>
       </c>
-      <c r="O37" s="4" t="s">
+      <c r="P37" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -9954,46 +13546,49 @@
         <v>12</v>
       </c>
       <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
         <v>70</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>15</v>
       </c>
-      <c r="E38" s="5">
+      <c r="F38" s="5">
         <v>5</v>
       </c>
-      <c r="F38" s="1">
+      <c r="G38" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G38" s="1">
+      <c r="H38" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H38" s="5">
+      <c r="I38" s="5">
         <v>14</v>
       </c>
-      <c r="I38" s="5">
+      <c r="J38" s="5">
         <v>10</v>
       </c>
-      <c r="J38" s="5">
+      <c r="K38" s="5">
         <v>16</v>
       </c>
-      <c r="K38" s="5">
+      <c r="L38" s="5">
         <v>29</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>0.65</v>
       </c>
-      <c r="M38" s="3">
+      <c r="N38" s="3">
         <v>0.16</v>
       </c>
-      <c r="N38" s="3">
+      <c r="O38" s="3">
         <v>0.3</v>
       </c>
-      <c r="O38" s="4" t="s">
+      <c r="P38" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -10001,46 +13596,49 @@
         <v>12</v>
       </c>
       <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
         <v>71</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>15</v>
       </c>
-      <c r="E39" s="5">
+      <c r="F39" s="5">
         <v>4</v>
       </c>
-      <c r="F39" s="1">
+      <c r="G39" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G39" s="1">
+      <c r="H39" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H39" s="5">
+      <c r="I39" s="5">
         <v>12</v>
       </c>
-      <c r="I39" s="5">
+      <c r="J39" s="5">
         <v>9</v>
       </c>
-      <c r="J39" s="5">
+      <c r="K39" s="5">
         <v>13</v>
       </c>
-      <c r="K39" s="5">
+      <c r="L39" s="5">
         <v>30</v>
       </c>
-      <c r="L39" s="2">
+      <c r="M39" s="2">
         <v>0.65</v>
       </c>
-      <c r="M39" s="3">
+      <c r="N39" s="3">
         <v>0.16</v>
       </c>
-      <c r="N39" s="3">
+      <c r="O39" s="3">
         <v>0.3</v>
       </c>
-      <c r="O39" s="4" t="s">
+      <c r="P39" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -10048,46 +13646,49 @@
         <v>159</v>
       </c>
       <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
         <v>72</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>15</v>
       </c>
-      <c r="E40" s="5">
+      <c r="F40" s="5">
         <v>5</v>
       </c>
-      <c r="F40" s="1">
+      <c r="G40" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G40" s="1">
+      <c r="H40" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H40" s="5">
+      <c r="I40" s="5">
         <v>14</v>
       </c>
-      <c r="I40" s="5">
+      <c r="J40" s="5">
         <v>10</v>
       </c>
-      <c r="J40" s="5">
+      <c r="K40" s="5">
         <v>16</v>
       </c>
-      <c r="K40" s="5">
+      <c r="L40" s="5">
         <v>30</v>
       </c>
-      <c r="L40" s="2">
+      <c r="M40" s="2">
         <v>0.63</v>
       </c>
-      <c r="M40" s="3">
+      <c r="N40" s="3">
         <v>0.16</v>
       </c>
-      <c r="N40" s="3">
+      <c r="O40" s="3">
         <v>0.3</v>
       </c>
-      <c r="O40" s="4" t="s">
+      <c r="P40" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -10095,46 +13696,49 @@
         <v>12</v>
       </c>
       <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
         <v>31</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>15</v>
       </c>
-      <c r="E41" s="5">
+      <c r="F41" s="5">
         <v>5</v>
       </c>
-      <c r="F41" s="1">
+      <c r="G41" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G41" s="1">
+      <c r="H41" s="1">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="H41" s="5">
+      <c r="I41" s="5">
         <v>13</v>
       </c>
-      <c r="I41" s="5">
+      <c r="J41" s="5">
         <v>9</v>
       </c>
-      <c r="J41" s="5">
+      <c r="K41" s="5">
         <v>15</v>
       </c>
-      <c r="K41" s="5">
+      <c r="L41" s="5">
         <v>32</v>
       </c>
-      <c r="L41" s="2">
+      <c r="M41" s="2">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>0.16</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>0.3</v>
       </c>
-      <c r="O41" s="4" t="s">
+      <c r="P41" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -10142,46 +13746,49 @@
         <v>12</v>
       </c>
       <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
         <v>32</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>15</v>
       </c>
-      <c r="E42" s="5">
+      <c r="F42" s="5">
         <v>6</v>
       </c>
-      <c r="F42" s="1">
+      <c r="G42" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G42" s="1">
+      <c r="H42" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H42" s="5">
+      <c r="I42" s="5">
         <v>15</v>
       </c>
-      <c r="I42" s="5">
+      <c r="J42" s="5">
         <v>11</v>
       </c>
-      <c r="J42" s="5">
+      <c r="K42" s="5">
         <v>17</v>
       </c>
-      <c r="K42" s="5">
+      <c r="L42" s="5">
         <v>32</v>
       </c>
-      <c r="L42" s="2">
+      <c r="M42" s="2">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>0.16</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>0.3</v>
       </c>
-      <c r="O42" s="4" t="s">
+      <c r="P42" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -10189,46 +13796,49 @@
         <v>12</v>
       </c>
       <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
         <v>30</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>15</v>
       </c>
-      <c r="E43" s="5">
+      <c r="F43" s="5">
         <v>4</v>
       </c>
-      <c r="F43" s="1">
+      <c r="G43" s="1">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G43" s="1">
+      <c r="H43" s="1">
         <v>0.03</v>
       </c>
-      <c r="H43" s="5">
+      <c r="I43" s="5">
         <v>11</v>
       </c>
-      <c r="I43" s="5">
+      <c r="J43" s="5">
         <v>8</v>
       </c>
-      <c r="J43" s="5">
+      <c r="K43" s="5">
         <v>12</v>
       </c>
-      <c r="K43" s="5">
+      <c r="L43" s="5">
         <v>32</v>
       </c>
-      <c r="L43" s="2">
+      <c r="M43" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>0.16</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>0.3</v>
       </c>
-      <c r="O43" s="4" t="s">
+      <c r="P43" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>24</v>
       </c>
@@ -10236,46 +13846,49 @@
         <v>12</v>
       </c>
       <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
         <v>73</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>15</v>
       </c>
-      <c r="E44" s="5">
+      <c r="F44" s="5">
         <v>4</v>
       </c>
-      <c r="F44" s="1">
+      <c r="G44" s="1">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G44" s="1">
+      <c r="H44" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="H44" s="5">
+      <c r="I44" s="5">
         <v>12</v>
       </c>
-      <c r="I44" s="5">
+      <c r="J44" s="5">
         <v>9</v>
       </c>
-      <c r="J44" s="5">
+      <c r="K44" s="5">
         <v>13</v>
       </c>
-      <c r="K44" s="5">
+      <c r="L44" s="5">
         <v>31</v>
       </c>
-      <c r="L44" s="2">
+      <c r="M44" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>0.16</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>0.3</v>
       </c>
-      <c r="O44" s="4" t="s">
+      <c r="P44" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -10283,46 +13896,49 @@
         <v>159</v>
       </c>
       <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
         <v>29</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>15</v>
       </c>
-      <c r="E45" s="5">
+      <c r="F45" s="5">
         <v>6</v>
       </c>
-      <c r="F45" s="1">
+      <c r="G45" s="1">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G45" s="1">
+      <c r="H45" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="H45" s="5">
+      <c r="I45" s="5">
         <v>15</v>
       </c>
-      <c r="I45" s="5">
+      <c r="J45" s="5">
         <v>11</v>
       </c>
-      <c r="J45" s="5">
+      <c r="K45" s="5">
         <v>17</v>
       </c>
-      <c r="K45" s="5">
+      <c r="L45" s="5">
         <v>30</v>
       </c>
-      <c r="L45" s="2">
+      <c r="M45" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>0.16</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>0.3</v>
       </c>
-      <c r="O45" s="4" t="s">
+      <c r="P45" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -10330,46 +13946,49 @@
         <v>159</v>
       </c>
       <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
         <v>16</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="5">
+      <c r="F46" s="5">
         <v>4</v>
       </c>
-      <c r="F46" s="1">
+      <c r="G46" s="1">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="G46" s="1">
+      <c r="H46" s="1">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="H46" s="5">
+      <c r="I46" s="5">
         <v>12</v>
       </c>
-      <c r="I46" s="5">
+      <c r="J46" s="5">
         <v>9</v>
       </c>
-      <c r="J46" s="5">
+      <c r="K46" s="5">
         <v>13</v>
       </c>
-      <c r="K46" s="5">
+      <c r="L46" s="5">
         <v>31</v>
       </c>
-      <c r="L46" s="2">
+      <c r="M46" s="2">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>0.16</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>0.3</v>
       </c>
-      <c r="O46" s="4" t="s">
+      <c r="P46" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>83</v>
       </c>
@@ -10377,46 +13996,49 @@
         <v>159</v>
       </c>
       <c r="C47" t="s">
+        <v>177</v>
+      </c>
+      <c r="D47" t="s">
         <v>74</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="5">
+      <c r="F47" s="5">
         <v>5</v>
       </c>
-      <c r="F47" s="1">
+      <c r="G47" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G47" s="1">
+      <c r="H47" s="1">
         <v>0.02</v>
       </c>
-      <c r="H47" s="5">
+      <c r="I47" s="5">
         <v>14</v>
       </c>
-      <c r="I47" s="5">
+      <c r="J47" s="5">
         <v>10</v>
       </c>
-      <c r="J47" s="5">
+      <c r="K47" s="5">
         <v>16</v>
       </c>
-      <c r="K47" s="5">
+      <c r="L47" s="5">
         <v>30</v>
       </c>
-      <c r="L47" s="2">
+      <c r="M47" s="2">
         <v>0.59</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>0.16</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>0.3</v>
       </c>
-      <c r="O47" s="4" t="s">
+      <c r="P47" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>84</v>
       </c>
@@ -10424,46 +14046,49 @@
         <v>159</v>
       </c>
       <c r="C48" t="s">
+        <v>177</v>
+      </c>
+      <c r="D48" t="s">
         <v>75</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="5">
+      <c r="F48" s="5">
         <v>8</v>
       </c>
-      <c r="F48" s="1">
+      <c r="G48" s="1">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G48" s="1">
+      <c r="H48" s="1">
         <v>0.03</v>
       </c>
-      <c r="H48" s="5">
+      <c r="I48" s="5">
         <v>20</v>
       </c>
-      <c r="I48" s="5">
+      <c r="J48" s="5">
         <v>15</v>
       </c>
-      <c r="J48" s="5">
+      <c r="K48" s="5">
         <v>23</v>
       </c>
-      <c r="K48" s="5">
+      <c r="L48" s="5">
         <v>30</v>
       </c>
-      <c r="L48" s="2">
+      <c r="M48" s="2">
         <v>0.62</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>0.16</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>0.3</v>
       </c>
-      <c r="O48" s="4" t="s">
+      <c r="P48" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:16">
       <c r="A49" t="s">
         <v>82</v>
       </c>
@@ -10471,46 +14096,49 @@
         <v>159</v>
       </c>
       <c r="C49" t="s">
+        <v>177</v>
+      </c>
+      <c r="D49" t="s">
         <v>76</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="5">
+      <c r="F49" s="5">
         <v>8</v>
       </c>
-      <c r="F49" s="1">
+      <c r="G49" s="1">
         <v>0.01</v>
       </c>
-      <c r="G49" s="1">
+      <c r="H49" s="1">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="H49" s="5">
+      <c r="I49" s="5">
         <v>21</v>
       </c>
-      <c r="I49" s="5">
+      <c r="J49" s="5">
         <v>15</v>
       </c>
-      <c r="J49" s="5">
+      <c r="K49" s="5">
         <v>24</v>
       </c>
-      <c r="K49" s="5">
+      <c r="L49" s="5">
         <v>30</v>
       </c>
-      <c r="L49" s="2">
+      <c r="M49" s="2">
         <v>0.64</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>0.16</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>0.3</v>
       </c>
-      <c r="O49" s="4" t="s">
+      <c r="P49" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:16">
       <c r="A50" t="s">
         <v>85</v>
       </c>
@@ -10518,46 +14146,49 @@
         <v>77</v>
       </c>
       <c r="C50" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" t="s">
         <v>78</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>15</v>
       </c>
-      <c r="E50" s="5">
+      <c r="F50" s="5">
         <v>5</v>
       </c>
-      <c r="F50" s="1">
+      <c r="G50" s="1">
         <v>1.4E-2</v>
       </c>
-      <c r="G50" s="1">
+      <c r="H50" s="1">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="H50" s="5">
+      <c r="I50" s="5">
         <v>13</v>
       </c>
-      <c r="I50" s="5">
+      <c r="J50" s="5">
         <v>9</v>
       </c>
-      <c r="J50" s="5">
+      <c r="K50" s="5">
         <v>15</v>
       </c>
-      <c r="K50" s="5">
+      <c r="L50" s="5">
         <v>30</v>
       </c>
-      <c r="L50" s="2">
+      <c r="M50" s="2">
         <v>0.63</v>
       </c>
-      <c r="M50" s="3">
+      <c r="N50" s="3">
         <v>0.16</v>
       </c>
-      <c r="N50" s="3">
+      <c r="O50" s="3">
         <v>0.3</v>
       </c>
-      <c r="O50" s="4" t="s">
+      <c r="P50" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:16">
       <c r="A51" t="s">
         <v>86</v>
       </c>
@@ -10565,46 +14196,49 @@
         <v>77</v>
       </c>
       <c r="C51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" t="s">
         <v>79</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>15</v>
       </c>
-      <c r="E51" s="5">
+      <c r="F51" s="5">
         <v>4</v>
       </c>
-      <c r="F51" s="1">
+      <c r="G51" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G51" s="1">
+      <c r="H51" s="1">
         <v>0.02</v>
       </c>
-      <c r="H51" s="5">
+      <c r="I51" s="5">
         <v>11</v>
       </c>
-      <c r="I51" s="5">
+      <c r="J51" s="5">
         <v>8</v>
       </c>
-      <c r="J51" s="5">
+      <c r="K51" s="5">
         <v>12</v>
       </c>
-      <c r="K51" s="5">
+      <c r="L51" s="5">
         <v>30</v>
       </c>
-      <c r="L51" s="2">
+      <c r="M51" s="2">
         <v>0.64</v>
       </c>
-      <c r="M51" s="3">
+      <c r="N51" s="3">
         <v>0.16</v>
       </c>
-      <c r="N51" s="3">
+      <c r="O51" s="3">
         <v>0.3</v>
       </c>
-      <c r="O51" s="4" t="s">
+      <c r="P51" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:16">
       <c r="A52" t="s">
         <v>87</v>
       </c>
@@ -10612,46 +14246,49 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" t="s">
         <v>80</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="5">
+      <c r="F52" s="5">
         <v>4</v>
       </c>
-      <c r="F52" s="1">
+      <c r="G52" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G52" s="1">
+      <c r="H52" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="H52" s="5">
+      <c r="I52" s="5">
         <v>12</v>
       </c>
-      <c r="I52" s="5">
+      <c r="J52" s="5">
         <v>9</v>
       </c>
-      <c r="J52" s="5">
+      <c r="K52" s="5">
         <v>13</v>
       </c>
-      <c r="K52" s="5">
+      <c r="L52" s="5">
         <v>30</v>
       </c>
-      <c r="L52" s="2">
+      <c r="M52" s="2">
         <v>0.65</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>0.16</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>0.3</v>
       </c>
-      <c r="O52" s="4" t="s">
+      <c r="P52" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:16">
       <c r="A53" t="s">
         <v>88</v>
       </c>
@@ -10659,46 +14296,49 @@
         <v>157</v>
       </c>
       <c r="C53" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" t="s">
         <v>81</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>15</v>
       </c>
-      <c r="E53" s="5">
+      <c r="F53" s="5">
         <v>4</v>
       </c>
-      <c r="F53" s="1">
+      <c r="G53" s="1">
         <v>2E-3</v>
       </c>
-      <c r="G53" s="1">
+      <c r="H53" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="H53" s="5">
+      <c r="I53" s="5">
         <v>12</v>
       </c>
-      <c r="I53" s="5">
+      <c r="J53" s="5">
         <v>9</v>
       </c>
-      <c r="J53" s="5">
+      <c r="K53" s="5">
         <v>13</v>
       </c>
-      <c r="K53" s="5">
+      <c r="L53" s="5">
         <v>30</v>
       </c>
-      <c r="L53" s="2">
+      <c r="M53" s="2">
         <v>0.64</v>
       </c>
-      <c r="M53" s="3">
+      <c r="N53" s="3">
         <v>0.16</v>
       </c>
-      <c r="N53" s="3">
+      <c r="O53" s="3">
         <v>0.3</v>
       </c>
-      <c r="O53" s="4" t="s">
+      <c r="P53" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:16">
       <c r="A54" t="s">
         <v>89</v>
       </c>
@@ -10706,46 +14346,49 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
+        <v>77</v>
+      </c>
+      <c r="D54" t="s">
         <v>90</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>15</v>
       </c>
-      <c r="E54" s="5">
+      <c r="F54" s="5">
         <v>6</v>
       </c>
-      <c r="F54" s="1">
+      <c r="G54" s="1">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G54" s="1">
+      <c r="H54" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="H54" s="5">
+      <c r="I54" s="5">
         <v>15</v>
       </c>
-      <c r="I54" s="5">
+      <c r="J54" s="5">
         <v>11</v>
       </c>
-      <c r="J54" s="5">
+      <c r="K54" s="5">
         <v>17</v>
       </c>
-      <c r="K54" s="5">
+      <c r="L54" s="5">
         <v>30</v>
       </c>
-      <c r="L54" s="2">
+      <c r="M54" s="2">
         <v>0.63</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>0.16</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>0.3</v>
       </c>
-      <c r="O54" s="4" t="s">
+      <c r="P54" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:16">
       <c r="A55" t="s">
         <v>91</v>
       </c>
@@ -10753,46 +14396,49 @@
         <v>157</v>
       </c>
       <c r="C55" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" t="s">
         <v>92</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>15</v>
       </c>
-      <c r="E55" s="5">
+      <c r="F55" s="5">
         <v>5</v>
       </c>
-      <c r="F55" s="1">
+      <c r="G55" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G55" s="1">
+      <c r="H55" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="H55" s="5">
+      <c r="I55" s="5">
         <v>14</v>
       </c>
-      <c r="I55" s="5">
+      <c r="J55" s="5">
         <v>10</v>
       </c>
-      <c r="J55" s="5">
+      <c r="K55" s="5">
         <v>16</v>
       </c>
-      <c r="K55" s="5">
+      <c r="L55" s="5">
         <v>30</v>
       </c>
-      <c r="L55" s="2">
+      <c r="M55" s="2">
         <v>0.65</v>
       </c>
-      <c r="M55" s="3">
+      <c r="N55" s="3">
         <v>0.16</v>
       </c>
-      <c r="N55" s="3">
+      <c r="O55" s="3">
         <v>0.3</v>
       </c>
-      <c r="O55" s="4" t="s">
+      <c r="P55" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:16">
       <c r="A56" t="s">
         <v>93</v>
       </c>
@@ -10800,46 +14446,49 @@
         <v>157</v>
       </c>
       <c r="C56" t="s">
+        <v>90</v>
+      </c>
+      <c r="D56" t="s">
         <v>98</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>15</v>
       </c>
-      <c r="E56" s="5">
+      <c r="F56" s="5">
         <v>4</v>
       </c>
-      <c r="F56" s="1">
+      <c r="G56" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G56" s="1">
+      <c r="H56" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H56" s="5">
+      <c r="I56" s="5">
         <v>12</v>
       </c>
-      <c r="I56" s="5">
+      <c r="J56" s="5">
         <v>9</v>
       </c>
-      <c r="J56" s="5">
+      <c r="K56" s="5">
         <v>13</v>
       </c>
-      <c r="K56" s="5">
+      <c r="L56" s="5">
         <v>30</v>
       </c>
-      <c r="L56" s="2">
+      <c r="M56" s="2">
         <v>0.65</v>
       </c>
-      <c r="M56" s="3">
+      <c r="N56" s="3">
         <v>0.16</v>
       </c>
-      <c r="N56" s="3">
+      <c r="O56" s="3">
         <v>0.3</v>
       </c>
-      <c r="O56" s="4" t="s">
+      <c r="P56" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:16">
       <c r="A57" t="s">
         <v>94</v>
       </c>
@@ -10847,46 +14496,49 @@
         <v>157</v>
       </c>
       <c r="C57" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" t="s">
         <v>99</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>15</v>
       </c>
-      <c r="E57" s="5">
+      <c r="F57" s="5">
         <v>5</v>
       </c>
-      <c r="F57" s="1">
+      <c r="G57" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G57" s="1">
+      <c r="H57" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="H57" s="5">
+      <c r="I57" s="5">
         <v>14</v>
       </c>
-      <c r="I57" s="5">
+      <c r="J57" s="5">
         <v>10</v>
       </c>
-      <c r="J57" s="5">
+      <c r="K57" s="5">
         <v>16</v>
       </c>
-      <c r="K57" s="5">
+      <c r="L57" s="5">
         <v>29</v>
       </c>
-      <c r="L57" s="2">
+      <c r="M57" s="2">
         <v>0.69</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>0.16</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>0.3</v>
       </c>
-      <c r="O57" s="4" t="s">
+      <c r="P57" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:16">
       <c r="A58" t="s">
         <v>95</v>
       </c>
@@ -10894,46 +14546,49 @@
         <v>157</v>
       </c>
       <c r="C58" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" t="s">
         <v>100</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>15</v>
       </c>
-      <c r="E58" s="5">
+      <c r="F58" s="5">
         <v>6</v>
       </c>
-      <c r="F58" s="1">
+      <c r="G58" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G58" s="1">
+      <c r="H58" s="1">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="H58" s="5">
+      <c r="I58" s="5">
         <v>15</v>
       </c>
-      <c r="I58" s="5">
+      <c r="J58" s="5">
         <v>11</v>
       </c>
-      <c r="J58" s="5">
+      <c r="K58" s="5">
         <v>17</v>
       </c>
-      <c r="K58" s="5">
+      <c r="L58" s="5">
         <v>32</v>
       </c>
-      <c r="L58" s="2">
+      <c r="M58" s="2">
         <v>0.66</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>0.16</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>0.3</v>
       </c>
-      <c r="O58" s="4" t="s">
+      <c r="P58" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:16">
       <c r="A59" t="s">
         <v>96</v>
       </c>
@@ -10941,46 +14596,49 @@
         <v>157</v>
       </c>
       <c r="C59" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" t="s">
         <v>101</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>15</v>
       </c>
-      <c r="E59" s="5">
+      <c r="F59" s="5">
         <v>6</v>
       </c>
-      <c r="F59" s="1">
+      <c r="G59" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G59" s="1">
+      <c r="H59" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H59" s="5">
+      <c r="I59" s="5">
         <v>16</v>
       </c>
-      <c r="I59" s="5">
+      <c r="J59" s="5">
         <v>12</v>
       </c>
-      <c r="J59" s="5">
+      <c r="K59" s="5">
         <v>18</v>
       </c>
-      <c r="K59" s="5">
+      <c r="L59" s="5">
         <v>30</v>
       </c>
-      <c r="L59" s="2">
+      <c r="M59" s="2">
         <v>0.65</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>0.16</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>0.3</v>
       </c>
-      <c r="O59" s="4" t="s">
+      <c r="P59" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:16">
       <c r="A60" t="s">
         <v>97</v>
       </c>
@@ -10988,93 +14646,99 @@
         <v>157</v>
       </c>
       <c r="C60" t="s">
+        <v>90</v>
+      </c>
+      <c r="D60" t="s">
         <v>102</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>15</v>
       </c>
-      <c r="E60" s="5">
+      <c r="F60" s="5">
         <v>8</v>
       </c>
-      <c r="F60" s="1">
+      <c r="G60" s="1">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G60" s="1">
+      <c r="H60" s="1">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="H60" s="5">
+      <c r="I60" s="5">
         <v>21</v>
       </c>
-      <c r="I60" s="5">
+      <c r="J60" s="5">
         <v>15</v>
       </c>
-      <c r="J60" s="5">
+      <c r="K60" s="5">
         <v>24</v>
       </c>
-      <c r="K60" s="5">
+      <c r="L60" s="5">
         <v>32</v>
       </c>
-      <c r="L60" s="2">
+      <c r="M60" s="2">
         <v>0.63</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>0.16</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>0.3</v>
       </c>
-      <c r="O60" s="4" t="s">
+      <c r="P60" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="16">
+    <row r="61" spans="1:16" ht="16">
       <c r="A61" t="s">
         <v>103</v>
       </c>
       <c r="B61" t="s">
         <v>155</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" t="s">
+        <v>177</v>
+      </c>
+      <c r="D61" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>15</v>
       </c>
-      <c r="E61" s="5">
+      <c r="F61" s="5">
         <v>6</v>
       </c>
-      <c r="F61" s="1">
+      <c r="G61" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G61" s="1">
+      <c r="H61" s="1">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="H61" s="5">
+      <c r="I61" s="5">
         <v>17</v>
       </c>
-      <c r="I61" s="5">
+      <c r="J61" s="5">
         <v>12</v>
       </c>
-      <c r="J61" s="5">
+      <c r="K61" s="5">
         <v>19</v>
       </c>
-      <c r="K61" s="5">
+      <c r="L61" s="5">
         <v>33</v>
       </c>
-      <c r="L61" s="2">
+      <c r="M61" s="2">
         <v>0.52</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>0.16</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>0.3</v>
       </c>
-      <c r="O61" s="4" t="s">
+      <c r="P61" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:16">
       <c r="A62" t="s">
         <v>104</v>
       </c>
@@ -11082,46 +14746,49 @@
         <v>155</v>
       </c>
       <c r="C62" t="s">
+        <v>177</v>
+      </c>
+      <c r="D62" t="s">
         <v>106</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>15</v>
       </c>
-      <c r="E62" s="5">
+      <c r="F62" s="5">
         <v>6</v>
       </c>
-      <c r="F62" s="1">
+      <c r="G62" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G62" s="1">
+      <c r="H62" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H62" s="5">
+      <c r="I62" s="5">
         <v>17</v>
       </c>
-      <c r="I62" s="5">
+      <c r="J62" s="5">
         <v>12</v>
       </c>
-      <c r="J62" s="5">
+      <c r="K62" s="5">
         <v>19</v>
       </c>
-      <c r="K62" s="5">
+      <c r="L62" s="5">
         <v>35</v>
       </c>
-      <c r="L62" s="2">
+      <c r="M62" s="2">
         <v>0.5</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>0.16</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>0.3</v>
       </c>
-      <c r="O62" s="4" t="s">
+      <c r="P62" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:16">
       <c r="A63" t="s">
         <v>112</v>
       </c>
@@ -11129,46 +14796,49 @@
         <v>153</v>
       </c>
       <c r="C63" t="s">
+        <v>175</v>
+      </c>
+      <c r="D63" t="s">
         <v>107</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>15</v>
       </c>
-      <c r="E63" s="5">
+      <c r="F63" s="5">
         <v>7</v>
       </c>
-      <c r="F63" s="1">
+      <c r="G63" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G63" s="1">
+      <c r="H63" s="1">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H63" s="5">
+      <c r="I63" s="5">
         <v>19</v>
       </c>
-      <c r="I63" s="5">
+      <c r="J63" s="5">
         <v>14</v>
       </c>
-      <c r="J63" s="5">
+      <c r="K63" s="5">
         <v>22</v>
       </c>
-      <c r="K63" s="5">
+      <c r="L63" s="5">
         <v>34</v>
       </c>
-      <c r="L63" s="2">
+      <c r="M63" s="2">
         <v>0.49</v>
       </c>
-      <c r="M63" s="3">
+      <c r="N63" s="3">
         <v>0.16</v>
       </c>
-      <c r="N63" s="3">
+      <c r="O63" s="3">
         <v>0.3</v>
       </c>
-      <c r="O63" s="4" t="s">
+      <c r="P63" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:16">
       <c r="A64" t="s">
         <v>113</v>
       </c>
@@ -11176,93 +14846,99 @@
         <v>153</v>
       </c>
       <c r="C64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D64" t="s">
         <v>108</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>15</v>
       </c>
-      <c r="E64" s="5">
+      <c r="F64" s="5">
         <v>8</v>
       </c>
-      <c r="F64" s="1">
+      <c r="G64" s="1">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G64" s="1">
+      <c r="H64" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="H64" s="5">
+      <c r="I64" s="5">
         <v>21</v>
       </c>
-      <c r="I64" s="5">
+      <c r="J64" s="5">
         <v>15</v>
       </c>
-      <c r="J64" s="5">
+      <c r="K64" s="5">
         <v>24</v>
       </c>
-      <c r="K64" s="5">
+      <c r="L64" s="5">
         <v>34</v>
       </c>
-      <c r="L64" s="2">
+      <c r="M64" s="2">
         <v>0.49</v>
       </c>
-      <c r="M64" s="3">
+      <c r="N64" s="3">
         <v>0.16</v>
       </c>
-      <c r="N64" s="3">
+      <c r="O64" s="3">
         <v>0.3</v>
       </c>
-      <c r="O64" s="4" t="s">
+      <c r="P64" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="16">
+    <row r="65" spans="1:16" ht="16">
       <c r="A65" t="s">
         <v>114</v>
       </c>
       <c r="B65" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" t="s">
+        <v>175</v>
+      </c>
+      <c r="D65" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>15</v>
       </c>
-      <c r="E65" s="5">
+      <c r="F65" s="5">
         <v>8</v>
       </c>
-      <c r="F65" s="1">
+      <c r="G65" s="1">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G65" s="1">
+      <c r="H65" s="1">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="H65" s="5">
+      <c r="I65" s="5">
         <v>21</v>
       </c>
-      <c r="I65" s="5">
+      <c r="J65" s="5">
         <v>15</v>
       </c>
-      <c r="J65" s="5">
+      <c r="K65" s="5">
         <v>24</v>
       </c>
-      <c r="K65" s="5">
+      <c r="L65" s="5">
         <v>34</v>
       </c>
-      <c r="L65" s="2">
+      <c r="M65" s="2">
         <v>0.52</v>
       </c>
-      <c r="M65" s="3">
+      <c r="N65" s="3">
         <v>0.16</v>
       </c>
-      <c r="N65" s="3">
+      <c r="O65" s="3">
         <v>0.3</v>
       </c>
-      <c r="O65" s="4" t="s">
+      <c r="P65" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:16">
       <c r="A66" t="s">
         <v>115</v>
       </c>
@@ -11270,46 +14946,49 @@
         <v>111</v>
       </c>
       <c r="C66" t="s">
+        <v>175</v>
+      </c>
+      <c r="D66" t="s">
         <v>110</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>15</v>
       </c>
-      <c r="E66" s="5">
+      <c r="F66" s="5">
         <v>8</v>
       </c>
-      <c r="F66" s="1">
+      <c r="G66" s="1">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G66" s="1">
+      <c r="H66" s="1">
         <v>1.2E-2</v>
       </c>
-      <c r="H66" s="5">
+      <c r="I66" s="5">
         <v>22</v>
       </c>
-      <c r="I66" s="5">
+      <c r="J66" s="5">
         <v>16</v>
       </c>
-      <c r="J66" s="5">
+      <c r="K66" s="5">
         <v>25</v>
       </c>
-      <c r="K66" s="5">
+      <c r="L66" s="5">
         <v>33</v>
       </c>
-      <c r="L66" s="2">
+      <c r="M66" s="2">
         <v>0.52</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>0.16</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>0.3</v>
       </c>
-      <c r="O66" s="4" t="s">
+      <c r="P66" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:16">
       <c r="A67" t="s">
         <v>116</v>
       </c>
@@ -11317,46 +14996,49 @@
         <v>111</v>
       </c>
       <c r="C67" t="s">
+        <v>175</v>
+      </c>
+      <c r="D67" t="s">
         <v>119</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>15</v>
       </c>
-      <c r="E67" s="5">
+      <c r="F67" s="5">
         <v>10</v>
       </c>
-      <c r="F67" s="1">
+      <c r="G67" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G67" s="1">
+      <c r="H67" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="H67" s="5">
+      <c r="I67" s="5">
         <v>25</v>
       </c>
-      <c r="I67" s="5">
+      <c r="J67" s="5">
         <v>19</v>
       </c>
-      <c r="J67" s="5">
+      <c r="K67" s="5">
         <v>29</v>
       </c>
-      <c r="K67" s="5">
+      <c r="L67" s="5">
         <v>32</v>
       </c>
-      <c r="L67" s="2">
+      <c r="M67" s="2">
         <v>0.54</v>
       </c>
-      <c r="M67" s="3">
+      <c r="N67" s="3">
         <v>0.16</v>
       </c>
-      <c r="N67" s="3">
+      <c r="O67" s="3">
         <v>0.3</v>
       </c>
-      <c r="O67" s="4" t="s">
+      <c r="P67" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:16">
       <c r="A68" t="s">
         <v>117</v>
       </c>
@@ -11364,46 +15046,49 @@
         <v>111</v>
       </c>
       <c r="C68" t="s">
+        <v>175</v>
+      </c>
+      <c r="D68" t="s">
         <v>120</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>15</v>
       </c>
-      <c r="E68" s="5">
+      <c r="F68" s="5">
         <v>9</v>
       </c>
-      <c r="F68" s="1">
+      <c r="G68" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G68" s="1">
+      <c r="H68" s="1">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H68" s="5">
+      <c r="I68" s="5">
         <v>23</v>
       </c>
-      <c r="I68" s="5">
+      <c r="J68" s="5">
         <v>17</v>
       </c>
-      <c r="J68" s="5">
+      <c r="K68" s="5">
         <v>26</v>
       </c>
-      <c r="K68" s="5">
+      <c r="L68" s="5">
         <v>31</v>
       </c>
-      <c r="L68" s="2">
+      <c r="M68" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M68" s="3">
+      <c r="N68" s="3">
         <v>0.16</v>
       </c>
-      <c r="N68" s="3">
+      <c r="O68" s="3">
         <v>0.3</v>
       </c>
-      <c r="O68" s="4" t="s">
+      <c r="P68" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:16">
       <c r="A69" t="s">
         <v>118</v>
       </c>
@@ -11411,936 +15096,1239 @@
         <v>111</v>
       </c>
       <c r="C69" t="s">
+        <v>175</v>
+      </c>
+      <c r="D69" t="s">
         <v>121</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>15</v>
       </c>
-      <c r="E69" s="5">
+      <c r="F69" s="5">
         <v>10</v>
       </c>
-      <c r="F69" s="1">
+      <c r="G69" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G69" s="1">
+      <c r="H69" s="1">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H69" s="5">
+      <c r="I69" s="5">
         <v>25</v>
       </c>
-      <c r="I69" s="5">
+      <c r="J69" s="5">
         <v>19</v>
       </c>
-      <c r="J69" s="5">
+      <c r="K69" s="5">
         <v>29</v>
       </c>
-      <c r="K69" s="5">
+      <c r="L69" s="5">
         <v>31</v>
       </c>
-      <c r="L69" s="2">
+      <c r="M69" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M69" s="3">
+      <c r="N69" s="3">
         <v>0.16</v>
       </c>
-      <c r="N69" s="3">
+      <c r="O69" s="3">
         <v>0.3</v>
       </c>
-      <c r="O69" s="4" t="s">
+      <c r="P69" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
+    <row r="70" spans="1:16">
       <c r="A70" t="s">
         <v>124</v>
       </c>
       <c r="B70" t="s">
         <v>151</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>144</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>15</v>
       </c>
-      <c r="E70" s="5">
+      <c r="F70" s="5">
         <v>7</v>
       </c>
-      <c r="F70" s="1">
+      <c r="G70" s="1">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="G70" s="1">
+      <c r="H70" s="1">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="H70" s="5">
+      <c r="I70" s="5">
         <v>18</v>
       </c>
-      <c r="I70" s="5">
+      <c r="J70" s="5">
         <v>13</v>
       </c>
-      <c r="J70" s="5">
+      <c r="K70" s="5">
         <v>20</v>
       </c>
-      <c r="K70" s="5">
+      <c r="L70" s="5">
         <v>27</v>
       </c>
-      <c r="L70" s="2">
+      <c r="M70" s="2">
         <v>0.8</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>0.16</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>0.3</v>
       </c>
-      <c r="O70" s="4" t="s">
+      <c r="P70" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:16">
       <c r="A71" t="s">
         <v>125</v>
       </c>
       <c r="B71" t="s">
         <v>151</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>144</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>15</v>
       </c>
-      <c r="E71" s="5">
+      <c r="F71" s="5">
         <v>7</v>
       </c>
-      <c r="F71" s="1">
+      <c r="G71" s="1">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="G71" s="1">
+      <c r="H71" s="1">
         <v>0.11899999999999999</v>
       </c>
-      <c r="H71" s="5">
+      <c r="I71" s="5">
         <v>19</v>
       </c>
-      <c r="I71" s="5">
+      <c r="J71" s="5">
         <v>14</v>
       </c>
-      <c r="J71" s="5">
+      <c r="K71" s="5">
         <v>22</v>
       </c>
-      <c r="K71" s="5">
+      <c r="L71" s="5">
         <v>27</v>
       </c>
-      <c r="L71" s="2">
+      <c r="M71" s="2">
         <v>0.8</v>
       </c>
-      <c r="M71" s="3">
+      <c r="N71" s="3">
         <v>0.16</v>
       </c>
-      <c r="N71" s="3">
+      <c r="O71" s="3">
         <v>0.3</v>
       </c>
-      <c r="O71" s="4" t="s">
+      <c r="P71" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:16">
       <c r="A72" t="s">
         <v>126</v>
       </c>
       <c r="B72" t="s">
         <v>151</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>144</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>15</v>
       </c>
-      <c r="E72" s="5">
+      <c r="F72" s="5">
         <v>6</v>
       </c>
-      <c r="F72" s="1">
+      <c r="G72" s="1">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G72" s="1">
+      <c r="H72" s="1">
         <v>0.121</v>
       </c>
-      <c r="H72" s="5">
+      <c r="I72" s="5">
         <v>17</v>
       </c>
-      <c r="I72" s="5">
+      <c r="J72" s="5">
         <v>12</v>
       </c>
-      <c r="J72" s="5">
+      <c r="K72" s="5">
         <v>20</v>
       </c>
-      <c r="K72" s="5">
+      <c r="L72" s="5">
         <v>27</v>
       </c>
-      <c r="L72" s="2">
+      <c r="M72" s="2">
         <v>0.8</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>0.16</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>0.3</v>
       </c>
-      <c r="O72" s="4" t="s">
+      <c r="P72" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:16">
       <c r="A73" t="s">
         <v>127</v>
       </c>
       <c r="B73" t="s">
         <v>151</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>144</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>15</v>
       </c>
-      <c r="E73" s="5">
+      <c r="F73" s="5">
         <v>7</v>
       </c>
-      <c r="F73" s="1">
+      <c r="G73" s="1">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G73" s="1">
+      <c r="H73" s="1">
         <v>0.115</v>
       </c>
-      <c r="H73" s="5">
+      <c r="I73" s="5">
         <v>18</v>
       </c>
-      <c r="I73" s="5">
+      <c r="J73" s="5">
         <v>13</v>
       </c>
-      <c r="J73" s="5">
+      <c r="K73" s="5">
         <v>20</v>
       </c>
-      <c r="K73" s="5">
+      <c r="L73" s="5">
         <v>27</v>
       </c>
-      <c r="L73" s="2">
+      <c r="M73" s="2">
         <v>0.79</v>
       </c>
-      <c r="M73" s="3">
+      <c r="N73" s="3">
         <v>0.16</v>
       </c>
-      <c r="N73" s="3">
+      <c r="O73" s="3">
         <v>0.3</v>
       </c>
-      <c r="O73" s="4" t="s">
+      <c r="P73" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:16">
       <c r="A74" t="s">
         <v>128</v>
       </c>
       <c r="B74" t="s">
         <v>151</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>144</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>15</v>
       </c>
-      <c r="E74" s="5">
+      <c r="F74" s="5">
         <v>7</v>
       </c>
-      <c r="F74" s="1">
+      <c r="G74" s="1">
         <v>2.7E-2</v>
       </c>
-      <c r="G74" s="1">
+      <c r="H74" s="1">
         <v>0.114</v>
       </c>
-      <c r="H74" s="5">
+      <c r="I74" s="5">
         <v>19</v>
       </c>
-      <c r="I74" s="5">
+      <c r="J74" s="5">
         <v>14</v>
       </c>
-      <c r="J74" s="5">
+      <c r="K74" s="5">
         <v>22</v>
       </c>
-      <c r="K74" s="5">
+      <c r="L74" s="5">
         <v>27</v>
       </c>
-      <c r="L74" s="2">
+      <c r="M74" s="2">
         <v>0.8</v>
       </c>
-      <c r="M74" s="3">
+      <c r="N74" s="3">
         <v>0.16</v>
       </c>
-      <c r="N74" s="3">
+      <c r="O74" s="3">
         <v>0.3</v>
       </c>
-      <c r="O74" s="4" t="s">
+      <c r="P74" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:16">
       <c r="A75" t="s">
         <v>129</v>
       </c>
       <c r="B75" t="s">
         <v>151</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>144</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>15</v>
       </c>
-      <c r="E75" s="5">
+      <c r="F75" s="5">
         <v>8</v>
       </c>
-      <c r="F75" s="1">
+      <c r="G75" s="1">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="G75" s="1">
+      <c r="H75" s="1">
         <v>0.109</v>
       </c>
-      <c r="H75" s="5">
+      <c r="I75" s="5">
         <v>20</v>
       </c>
-      <c r="I75" s="5">
+      <c r="J75" s="5">
         <v>15</v>
       </c>
-      <c r="J75" s="5">
+      <c r="K75" s="5">
         <v>23</v>
       </c>
-      <c r="K75" s="5">
+      <c r="L75" s="5">
         <v>27</v>
       </c>
-      <c r="L75" s="2">
+      <c r="M75" s="2">
         <v>0.8</v>
       </c>
-      <c r="M75" s="3">
+      <c r="N75" s="3">
         <v>0.16</v>
       </c>
-      <c r="N75" s="3">
+      <c r="O75" s="3">
         <v>0.3</v>
       </c>
-      <c r="O75" s="4" t="s">
+      <c r="P75" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:16">
       <c r="A76" t="s">
         <v>130</v>
       </c>
       <c r="B76" t="s">
         <v>151</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>144</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>15</v>
       </c>
-      <c r="E76" s="5">
+      <c r="F76" s="5">
         <v>9</v>
       </c>
-      <c r="F76" s="1">
+      <c r="G76" s="1">
         <v>2.3E-2</v>
       </c>
-      <c r="G76" s="1">
+      <c r="H76" s="1">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="H76" s="5">
+      <c r="I76" s="5">
         <v>23</v>
       </c>
-      <c r="I76" s="5">
+      <c r="J76" s="5">
         <v>17</v>
       </c>
-      <c r="J76" s="5">
+      <c r="K76" s="5">
         <v>26</v>
       </c>
-      <c r="K76" s="5">
+      <c r="L76" s="5">
         <v>27</v>
       </c>
-      <c r="L76" s="2">
+      <c r="M76" s="2">
         <v>0.79</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>0.16</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>0.3</v>
       </c>
-      <c r="O76" s="4" t="s">
+      <c r="P76" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:16">
       <c r="A77" t="s">
         <v>131</v>
       </c>
       <c r="B77" t="s">
         <v>151</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>144</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="5">
+      <c r="F77" s="5">
         <v>9</v>
       </c>
-      <c r="F77" s="1">
+      <c r="G77" s="1">
         <v>0.02</v>
       </c>
-      <c r="G77" s="1">
+      <c r="H77" s="1">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="H77" s="5">
+      <c r="I77" s="5">
         <v>24</v>
       </c>
-      <c r="I77" s="5">
+      <c r="J77" s="5">
         <v>18</v>
-      </c>
-      <c r="J77" s="5">
-        <v>27</v>
       </c>
       <c r="K77" s="5">
         <v>27</v>
       </c>
-      <c r="L77" s="2">
+      <c r="L77" s="5">
+        <v>27</v>
+      </c>
+      <c r="M77" s="2">
         <v>0.79</v>
       </c>
-      <c r="M77" s="3">
+      <c r="N77" s="3">
         <v>0.16</v>
       </c>
-      <c r="N77" s="3">
+      <c r="O77" s="3">
         <v>0.3</v>
       </c>
-      <c r="O77" s="4" t="s">
+      <c r="P77" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:16">
       <c r="A78" t="s">
         <v>132</v>
       </c>
       <c r="B78" t="s">
         <v>151</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>144</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>15</v>
       </c>
-      <c r="E78" s="5">
+      <c r="F78" s="5">
         <v>7</v>
       </c>
-      <c r="F78" s="1">
+      <c r="G78" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="G78" s="1">
+      <c r="H78" s="1">
         <v>0.10199999999999999</v>
       </c>
-      <c r="H78" s="5">
+      <c r="I78" s="5">
         <v>19</v>
       </c>
-      <c r="I78" s="5">
+      <c r="J78" s="5">
         <v>14</v>
       </c>
-      <c r="J78" s="5">
+      <c r="K78" s="5">
         <v>22</v>
       </c>
-      <c r="K78" s="5">
+      <c r="L78" s="5">
         <v>27</v>
       </c>
-      <c r="L78" s="2">
+      <c r="M78" s="2">
         <v>0.76</v>
       </c>
-      <c r="M78" s="3">
+      <c r="N78" s="3">
         <v>0.16</v>
       </c>
-      <c r="N78" s="3">
+      <c r="O78" s="3">
         <v>0.3</v>
       </c>
-      <c r="O78" s="4" t="s">
+      <c r="P78" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:16">
       <c r="A79" t="s">
         <v>133</v>
       </c>
       <c r="B79" t="s">
         <v>151</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>146</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>15</v>
       </c>
-      <c r="E79" s="5">
+      <c r="F79" s="5">
         <v>6</v>
       </c>
-      <c r="F79" s="1">
+      <c r="G79" s="1">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="G79" s="1">
+      <c r="H79" s="1">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="H79" s="5">
+      <c r="I79" s="5">
         <v>17</v>
       </c>
-      <c r="I79" s="5">
+      <c r="J79" s="5">
         <v>12</v>
       </c>
-      <c r="J79" s="5">
+      <c r="K79" s="5">
         <v>19</v>
       </c>
-      <c r="K79" s="5">
+      <c r="L79" s="5">
         <v>27</v>
       </c>
-      <c r="L79" s="2">
+      <c r="M79" s="2">
         <v>0.8</v>
       </c>
-      <c r="M79" s="3">
+      <c r="N79" s="3">
         <v>0.16</v>
       </c>
-      <c r="N79" s="3">
+      <c r="O79" s="3">
         <v>0.3</v>
       </c>
-      <c r="O79" s="4" t="s">
+      <c r="P79" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
         <v>134</v>
       </c>
       <c r="B80" t="s">
         <v>151</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>146</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>15</v>
       </c>
-      <c r="E80" s="5">
+      <c r="F80" s="5">
         <v>2</v>
-      </c>
-      <c r="F80" s="1">
-        <v>0</v>
       </c>
       <c r="G80" s="1">
         <v>0</v>
       </c>
-      <c r="H80" s="5">
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+      <c r="I80" s="5">
         <v>6</v>
       </c>
-      <c r="I80" s="5">
+      <c r="J80" s="5">
         <v>4</v>
       </c>
-      <c r="J80" s="5">
+      <c r="K80" s="5">
         <v>6</v>
       </c>
-      <c r="K80" s="5">
+      <c r="L80" s="5">
         <v>27</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>0.77</v>
       </c>
-      <c r="M80" s="3">
+      <c r="N80" s="3">
         <v>0.16</v>
       </c>
-      <c r="N80" s="3">
+      <c r="O80" s="3">
         <v>0.3</v>
       </c>
-      <c r="O80" s="4" t="s">
+      <c r="P80" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
+    <row r="81" spans="1:16">
       <c r="A81" t="s">
         <v>135</v>
       </c>
       <c r="B81" t="s">
         <v>151</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>146</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>15</v>
       </c>
-      <c r="E81" s="5">
+      <c r="F81" s="5">
         <v>2</v>
-      </c>
-      <c r="F81" s="1">
-        <v>0</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
       </c>
-      <c r="H81" s="5">
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="5">
         <v>6</v>
       </c>
-      <c r="I81" s="5">
+      <c r="J81" s="5">
         <v>4</v>
       </c>
-      <c r="J81" s="5">
+      <c r="K81" s="5">
         <v>6</v>
       </c>
-      <c r="K81" s="5">
+      <c r="L81" s="5">
         <v>27</v>
       </c>
-      <c r="L81" s="2">
+      <c r="M81" s="2">
         <v>0.73</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>0.16</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>0.3</v>
       </c>
-      <c r="O81" s="4" t="s">
+      <c r="P81" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:16">
       <c r="A82" t="s">
         <v>136</v>
       </c>
       <c r="B82" t="s">
         <v>151</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>146</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>15</v>
       </c>
-      <c r="E82" s="5">
+      <c r="F82" s="5">
         <v>2</v>
       </c>
-      <c r="F82" s="1">
+      <c r="G82" s="1">
         <v>2E-3</v>
       </c>
-      <c r="G82" s="1">
+      <c r="H82" s="1">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="H82" s="5">
+      <c r="I82" s="5">
         <v>5</v>
       </c>
-      <c r="I82" s="5">
+      <c r="J82" s="5">
         <v>3</v>
       </c>
-      <c r="J82" s="5">
+      <c r="K82" s="5">
         <v>5</v>
       </c>
-      <c r="K82" s="5">
+      <c r="L82" s="5">
         <v>27</v>
       </c>
-      <c r="L82" s="2">
+      <c r="M82" s="2">
         <v>0.71</v>
       </c>
-      <c r="M82" s="3">
+      <c r="N82" s="3">
         <v>0.16</v>
       </c>
-      <c r="N82" s="3">
+      <c r="O82" s="3">
         <v>0.3</v>
       </c>
-      <c r="O82" s="4" t="s">
+      <c r="P82" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:16">
       <c r="A83" t="s">
         <v>137</v>
       </c>
       <c r="B83" t="s">
         <v>151</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>146</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>15</v>
       </c>
-      <c r="E83" s="5">
+      <c r="F83" s="5">
         <v>2</v>
       </c>
-      <c r="F83" s="1">
+      <c r="G83" s="1">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G83" s="1">
+      <c r="H83" s="1">
         <v>0.03</v>
       </c>
-      <c r="H83" s="5">
+      <c r="I83" s="5">
         <v>5</v>
       </c>
-      <c r="I83" s="5">
+      <c r="J83" s="5">
         <v>3</v>
       </c>
-      <c r="J83" s="5">
+      <c r="K83" s="5">
         <v>5</v>
       </c>
-      <c r="K83" s="5">
+      <c r="L83" s="5">
         <v>27</v>
       </c>
-      <c r="L83" s="2">
+      <c r="M83" s="2">
         <v>0.71</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>0.16</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>0.3</v>
       </c>
-      <c r="O83" s="4" t="s">
+      <c r="P83" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="84" spans="1:15">
+    <row r="84" spans="1:16">
       <c r="A84" t="s">
         <v>138</v>
       </c>
       <c r="B84" t="s">
         <v>151</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>146</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>15</v>
       </c>
-      <c r="E84" s="5">
+      <c r="F84" s="5">
         <v>2</v>
       </c>
-      <c r="F84" s="1">
+      <c r="G84" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G84" s="1">
+      <c r="H84" s="1">
         <v>1.6E-2</v>
       </c>
-      <c r="H84" s="5">
+      <c r="I84" s="5">
         <v>5</v>
       </c>
-      <c r="I84" s="5">
+      <c r="J84" s="5">
         <v>3</v>
       </c>
-      <c r="J84" s="5">
+      <c r="K84" s="5">
         <v>5</v>
       </c>
-      <c r="K84" s="5">
+      <c r="L84" s="5">
         <v>27</v>
       </c>
-      <c r="L84" s="2">
+      <c r="M84" s="2">
         <v>0.69</v>
       </c>
-      <c r="M84" s="3">
+      <c r="N84" s="3">
         <v>0.16</v>
       </c>
-      <c r="N84" s="3">
+      <c r="O84" s="3">
         <v>0.3</v>
       </c>
-      <c r="O84" s="4" t="s">
+      <c r="P84" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="85" spans="1:15">
+    <row r="85" spans="1:16">
       <c r="A85" t="s">
         <v>139</v>
       </c>
       <c r="B85" t="s">
         <v>151</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>148</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>15</v>
       </c>
-      <c r="E85" s="5">
+      <c r="F85" s="5">
         <v>8</v>
       </c>
-      <c r="F85" s="1">
+      <c r="G85" s="1">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="G85" s="1">
+      <c r="H85" s="1">
         <v>0.17699999999999999</v>
       </c>
-      <c r="H85" s="5">
+      <c r="I85" s="5">
         <v>10</v>
       </c>
-      <c r="I85" s="5">
+      <c r="J85" s="5">
         <v>7</v>
       </c>
-      <c r="J85" s="5">
+      <c r="K85" s="5">
         <v>11</v>
       </c>
-      <c r="K85" s="5">
+      <c r="L85" s="5">
         <v>27</v>
       </c>
-      <c r="L85" s="2">
+      <c r="M85" s="2">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M85" s="3">
+      <c r="N85" s="3">
         <v>0.16</v>
       </c>
-      <c r="N85" s="3">
+      <c r="O85" s="3">
         <v>0.3</v>
       </c>
-      <c r="O85" s="4" t="s">
+      <c r="P85" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="86" spans="1:15">
+    <row r="86" spans="1:16">
       <c r="A86" t="s">
         <v>140</v>
       </c>
       <c r="B86" t="s">
         <v>151</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>148</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>15</v>
       </c>
-      <c r="E86" s="5">
+      <c r="F86" s="5">
         <v>11</v>
       </c>
-      <c r="F86" s="1">
+      <c r="G86" s="1">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="G86" s="1">
+      <c r="H86" s="1">
         <v>0.216</v>
       </c>
-      <c r="H86" s="5">
+      <c r="I86" s="5">
         <v>10</v>
       </c>
-      <c r="I86" s="5">
+      <c r="J86" s="5">
         <v>7</v>
       </c>
-      <c r="J86" s="5">
+      <c r="K86" s="5">
         <v>11</v>
       </c>
-      <c r="K86" s="5">
+      <c r="L86" s="5">
         <v>27</v>
       </c>
-      <c r="L86" s="2">
+      <c r="M86" s="2">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M86" s="3">
+      <c r="N86" s="3">
         <v>0.16</v>
       </c>
-      <c r="N86" s="3">
+      <c r="O86" s="3">
         <v>0.3</v>
       </c>
-      <c r="O86" s="4" t="s">
+      <c r="P86" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="87" spans="1:15">
+    <row r="87" spans="1:16">
       <c r="A87" t="s">
         <v>141</v>
       </c>
       <c r="B87" t="s">
         <v>151</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>148</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>15</v>
       </c>
-      <c r="E87" s="5">
+      <c r="F87" s="5">
         <v>17</v>
       </c>
-      <c r="F87" s="1">
+      <c r="G87" s="1">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="G87" s="1">
+      <c r="H87" s="1">
         <v>0.28199999999999997</v>
       </c>
-      <c r="H87" s="5">
+      <c r="I87" s="5">
         <v>10</v>
       </c>
-      <c r="I87" s="5">
+      <c r="J87" s="5">
         <v>7</v>
       </c>
-      <c r="J87" s="5">
+      <c r="K87" s="5">
         <v>11</v>
       </c>
-      <c r="K87" s="5">
+      <c r="L87" s="5">
         <v>27</v>
       </c>
-      <c r="L87" s="2">
+      <c r="M87" s="2">
         <v>0.54</v>
       </c>
-      <c r="M87" s="3">
+      <c r="N87" s="3">
         <v>0.16</v>
       </c>
-      <c r="N87" s="3">
+      <c r="O87" s="3">
         <v>0.3</v>
       </c>
-      <c r="O87" s="4" t="s">
+      <c r="P87" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="88" spans="1:15">
+    <row r="88" spans="1:16">
       <c r="A88" t="s">
         <v>142</v>
       </c>
       <c r="B88" t="s">
         <v>151</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>150</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>15</v>
       </c>
-      <c r="E88" s="5">
+      <c r="F88" s="5">
         <v>12</v>
       </c>
-      <c r="F88" s="1">
+      <c r="G88" s="1">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="G88" s="1">
+      <c r="H88" s="1">
         <v>0.218</v>
       </c>
-      <c r="H88" s="5">
+      <c r="I88" s="5">
         <v>16</v>
       </c>
-      <c r="I88" s="5">
+      <c r="J88" s="5">
         <v>12</v>
       </c>
-      <c r="J88" s="5">
+      <c r="K88" s="5">
         <v>18</v>
       </c>
-      <c r="K88" s="5">
+      <c r="L88" s="5">
         <v>29</v>
       </c>
-      <c r="L88" s="2">
+      <c r="M88" s="2">
         <v>0.73</v>
       </c>
-      <c r="M88" s="3">
+      <c r="N88" s="3">
         <v>0.16</v>
       </c>
-      <c r="N88" s="3">
+      <c r="O88" s="3">
         <v>0.3</v>
       </c>
-      <c r="O88" s="4" t="s">
+      <c r="P88" s="4" t="s">
         <v>123</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
+      <c r="A89" t="s">
+        <v>179</v>
+      </c>
+      <c r="B89" t="s">
+        <v>178</v>
+      </c>
+      <c r="C89" t="s">
+        <v>186</v>
+      </c>
+      <c r="D89" t="s">
+        <v>187</v>
+      </c>
+      <c r="E89" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" s="5">
+        <v>5</v>
+      </c>
+      <c r="G89" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H89" s="1">
+        <v>1.2E-2</v>
+      </c>
+      <c r="I89" s="5">
+        <v>13</v>
+      </c>
+      <c r="J89" s="5">
+        <v>9</v>
+      </c>
+      <c r="K89" s="5">
+        <v>15</v>
+      </c>
+      <c r="L89" s="5">
+        <v>33</v>
+      </c>
+      <c r="M89" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P89" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
+      <c r="A90" t="s">
+        <v>180</v>
+      </c>
+      <c r="B90" t="s">
+        <v>178</v>
+      </c>
+      <c r="C90" t="s">
+        <v>186</v>
+      </c>
+      <c r="D90" t="s">
+        <v>188</v>
+      </c>
+      <c r="E90" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" s="5">
+        <v>4</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0</v>
+      </c>
+      <c r="I90" s="5">
+        <v>10</v>
+      </c>
+      <c r="J90" s="5">
+        <v>7</v>
+      </c>
+      <c r="K90" s="5">
+        <v>11</v>
+      </c>
+      <c r="L90" s="5">
+        <v>32</v>
+      </c>
+      <c r="M90" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N90" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="O90" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P90" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
+      <c r="A91" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91" t="s">
+        <v>178</v>
+      </c>
+      <c r="C91" t="s">
+        <v>186</v>
+      </c>
+      <c r="D91" t="s">
+        <v>189</v>
+      </c>
+      <c r="E91" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" s="5">
+        <v>4</v>
+      </c>
+      <c r="G91" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H91" s="1">
+        <v>1.2E-2</v>
+      </c>
+      <c r="I91" s="5">
+        <v>10</v>
+      </c>
+      <c r="J91" s="5">
+        <v>7</v>
+      </c>
+      <c r="K91" s="5">
+        <v>11</v>
+      </c>
+      <c r="L91" s="5">
+        <v>31</v>
+      </c>
+      <c r="M91" s="2">
+        <v>0.61</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P91" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
+      <c r="A92" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" t="s">
+        <v>178</v>
+      </c>
+      <c r="C92" t="s">
+        <v>186</v>
+      </c>
+      <c r="D92" t="s">
+        <v>190</v>
+      </c>
+      <c r="E92" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92" s="5">
+        <v>4</v>
+      </c>
+      <c r="G92" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H92" s="1">
+        <v>1.2E-2</v>
+      </c>
+      <c r="I92" s="5">
+        <v>10</v>
+      </c>
+      <c r="J92" s="5">
+        <v>7</v>
+      </c>
+      <c r="K92" s="5">
+        <v>11</v>
+      </c>
+      <c r="L92" s="5">
+        <v>31</v>
+      </c>
+      <c r="M92" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P92" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
+      <c r="A93" t="s">
+        <v>183</v>
+      </c>
+      <c r="B93" t="s">
+        <v>178</v>
+      </c>
+      <c r="C93" t="s">
+        <v>186</v>
+      </c>
+      <c r="D93" t="s">
+        <v>191</v>
+      </c>
+      <c r="E93" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93" s="5">
+        <v>4</v>
+      </c>
+      <c r="G93" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H93" s="1">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="I93" s="5">
+        <v>10</v>
+      </c>
+      <c r="J93" s="5">
+        <v>7</v>
+      </c>
+      <c r="K93" s="5">
+        <v>11</v>
+      </c>
+      <c r="L93" s="5">
+        <v>30</v>
+      </c>
+      <c r="M93" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P93" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
+      <c r="A94" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" t="s">
+        <v>178</v>
+      </c>
+      <c r="C94" t="s">
+        <v>186</v>
+      </c>
+      <c r="D94" t="s">
+        <v>192</v>
+      </c>
+      <c r="E94" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="5">
+        <v>4</v>
+      </c>
+      <c r="G94" s="1">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="H94" s="1">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I94" s="5">
+        <v>12</v>
+      </c>
+      <c r="J94" s="5">
+        <v>9</v>
+      </c>
+      <c r="K94" s="5">
+        <v>13</v>
+      </c>
+      <c r="L94" s="5">
+        <v>30</v>
+      </c>
+      <c r="M94" s="2">
+        <v>0.67</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="P94" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -12351,12 +16339,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B281C63B-8C58-9F41-8F1B-004B6747AE34}">
-  <dimension ref="B5:G82"/>
+  <dimension ref="B5:G132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -12687,9 +16676,204 @@
         <v>0.29999999999999993</v>
       </c>
     </row>
+    <row r="112" spans="2:3">
+      <c r="B112" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C112" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C114" t="s">
+        <v>166</v>
+      </c>
+      <c r="D114" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C115" s="1">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="D115" s="1">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C116" s="1">
+        <v>2.1333333333333333E-2</v>
+      </c>
+      <c r="D116" s="1">
+        <v>15.333333333333334</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C117" s="1">
+        <v>3.5900000000000008E-2</v>
+      </c>
+      <c r="D117" s="1">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C118" s="1">
+        <v>2.863636363636364E-2</v>
+      </c>
+      <c r="D118" s="1">
+        <v>13.363636363636363</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C119" s="1">
+        <v>2.98E-2</v>
+      </c>
+      <c r="D119" s="1">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C120" s="1">
+        <v>2.1857142857142856E-2</v>
+      </c>
+      <c r="D120" s="1">
+        <v>22.285714285714285</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C121" s="1">
+        <v>1.3666666666666666E-2</v>
+      </c>
+      <c r="D121" s="1">
+        <v>10.833333333333334</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="B122" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C122" s="1">
+        <v>2.5999999999999995E-2</v>
+      </c>
+      <c r="D122" s="1">
+        <v>14.92</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C126" s="1">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="D126" s="1">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C127" s="1">
+        <v>2.1333333333333333E-2</v>
+      </c>
+      <c r="D127" s="1">
+        <v>15.333333333333334</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C128" s="1">
+        <v>3.5900000000000008E-2</v>
+      </c>
+      <c r="D128" s="1">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C129" s="1">
+        <v>2.863636363636364E-2</v>
+      </c>
+      <c r="D129" s="1">
+        <v>13.363636363636363</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C130" s="1">
+        <v>2.98E-2</v>
+      </c>
+      <c r="D130" s="1">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C131" s="1">
+        <v>2.1857142857142856E-2</v>
+      </c>
+      <c r="D131" s="1">
+        <v>22.285714285714285</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C132" s="1">
+        <v>1.3666666666666666E-2</v>
+      </c>
+      <c r="D132" s="1">
+        <v>10.833333333333334</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
--- a/db/A7XLK-1001-TVOC-20210720.xlsx
+++ b/db/A7XLK-1001-TVOC-20210720.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38497270-BE88-FD4C-8966-A99149B9C68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64346EE-CC27-4744-B735-FBE1EFEC453C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4720" yWindow="1420" windowWidth="29360" windowHeight="18360" activeTab="1" xr2:uid="{11F38E42-6FA0-9247-A4F3-693D0F2BA4D6}"/>
+    <workbookView xWindow="3260" yWindow="2100" windowWidth="29360" windowHeight="18360" xr2:uid="{11F38E42-6FA0-9247-A4F3-693D0F2BA4D6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Analysis" sheetId="2" r:id="rId2"/>
+    <sheet name="工作表1" sheetId="3" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId2"/>
+    <sheet name="Analysis" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="25" r:id="rId3"/>
-    <pivotCache cacheId="32" r:id="rId4"/>
+    <pivotCache cacheId="33" r:id="rId4"/>
+    <pivotCache cacheId="37" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="201">
   <si>
     <t>No</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -745,16 +746,27 @@
   <si>
     <t>PM2.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(多重項目)</t>
+  </si>
+  <si>
+    <t>平均值 - Humidity</t>
+  </si>
+  <si>
+    <t>平均值 - Temperature</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="#,##0.000_ "/>
     <numFmt numFmtId="177" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="0.0%"/>
+    <numFmt numFmtId="180" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -795,7 +807,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -823,6 +835,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -841,6 +859,782 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[A7XLK-1001-TVOC-20210720.xlsx]工作表1!樞紐分析表5</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表1!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平均值 - Humidity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表1!$A$4:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>文化一路</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青路</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>華亞二路</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>華亞三路</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>樂善二路</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>樂學路</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>樟腦寮步道</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表1!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.63800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.65499999999999992</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.64200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.60727272727272741</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.57400000000000007</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5257142857142858</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.62166666666666659</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-582F-F44E-BA7A-366AED3EC286}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="29"/>
+        <c:overlap val="-52"/>
+        <c:axId val="924574079"/>
+        <c:axId val="1365882479"/>
+      </c:barChart>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>工作表1!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>平均值 - Temperature</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表1!$A$4:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>文化一路</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>文青路</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>華亞二路</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>華亞三路</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>樂善二路</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>樂學路</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>樟腦寮步道</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表1!$C$4:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0_ </c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32.714285714285715</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31.166666666666668</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-582F-F44E-BA7A-366AED3EC286}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="225"/>
+        <c:overlap val="-9"/>
+        <c:axId val="959410991"/>
+        <c:axId val="939662863"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="924574079"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1365882479"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1365882479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.8"/>
+          <c:min val="0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="924574079"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="939662863"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="40"/>
+          <c:min val="10"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.0_ " sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="959410991"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="959410991"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="939662863"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -1712,7 +2506,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -2560,7 +3354,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -3792,7 +4586,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-TW"/>
@@ -4461,6 +5255,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="942298911"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -4670,6 +5465,46 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6721,7 +7556,551 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24EAAE28-59DA-7A49-A549-751FB64A1F3C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -7285,10 +8664,46 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4" maxValue="29"/>
     </cacheField>
     <cacheField name="Temperature" numFmtId="178">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="27" maxValue="35"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="27" maxValue="35" count="9">
+        <n v="30"/>
+        <n v="29"/>
+        <n v="28"/>
+        <n v="32"/>
+        <n v="31"/>
+        <n v="33"/>
+        <n v="35"/>
+        <n v="34"/>
+        <n v="27"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Humidity" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.49" maxValue="0.8"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.49" maxValue="0.8" count="25">
+        <n v="0.69"/>
+        <n v="0.65"/>
+        <n v="0.67"/>
+        <n v="0.68"/>
+        <n v="0.7"/>
+        <n v="0.71"/>
+        <n v="0.66"/>
+        <n v="0.64"/>
+        <n v="0.62"/>
+        <n v="0.63"/>
+        <n v="0.55000000000000004"/>
+        <n v="0.56000000000000005"/>
+        <n v="0.56999999999999995"/>
+        <n v="0.59"/>
+        <n v="0.52"/>
+        <n v="0.5"/>
+        <n v="0.49"/>
+        <n v="0.54"/>
+        <n v="0.8"/>
+        <n v="0.79"/>
+        <n v="0.76"/>
+        <n v="0.77"/>
+        <n v="0.73"/>
+        <n v="0.57999999999999996"/>
+        <n v="0.61"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="TVOCS-L1" numFmtId="177">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.16" maxValue="0.16"/>
@@ -8810,8 +10225,8 @@
     <x v="0"/>
     <n v="4"/>
     <n v="6"/>
-    <n v="30"/>
-    <n v="0.69"/>
+    <x v="0"/>
+    <x v="0"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -8828,8 +10243,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="30"/>
-    <n v="0.69"/>
+    <x v="0"/>
+    <x v="0"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -8846,8 +10261,8 @@
     <x v="2"/>
     <n v="3"/>
     <n v="4"/>
-    <n v="29"/>
-    <n v="0.65"/>
+    <x v="1"/>
+    <x v="1"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -8864,8 +10279,8 @@
     <x v="2"/>
     <n v="3"/>
     <n v="4"/>
-    <n v="29"/>
-    <n v="0.67"/>
+    <x v="1"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -8882,8 +10297,8 @@
     <x v="2"/>
     <n v="3"/>
     <n v="4"/>
-    <n v="29"/>
-    <n v="0.67"/>
+    <x v="1"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -8900,8 +10315,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="29"/>
-    <n v="0.67"/>
+    <x v="1"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -8918,8 +10333,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="29"/>
-    <n v="0.67"/>
+    <x v="1"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -8936,8 +10351,8 @@
     <x v="2"/>
     <n v="3"/>
     <n v="4"/>
-    <n v="29"/>
-    <n v="0.68"/>
+    <x v="1"/>
+    <x v="3"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -8954,8 +10369,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="30"/>
-    <n v="0.69"/>
+    <x v="0"/>
+    <x v="0"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -8972,8 +10387,8 @@
     <x v="2"/>
     <n v="3"/>
     <n v="4"/>
-    <n v="29"/>
-    <n v="0.68"/>
+    <x v="1"/>
+    <x v="3"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -8990,8 +10405,8 @@
     <x v="2"/>
     <n v="3"/>
     <n v="4"/>
-    <n v="30"/>
-    <n v="0.68"/>
+    <x v="0"/>
+    <x v="3"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9008,8 +10423,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="29"/>
-    <n v="0.67"/>
+    <x v="1"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9026,8 +10441,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="29"/>
-    <n v="0.7"/>
+    <x v="1"/>
+    <x v="4"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9044,8 +10459,8 @@
     <x v="0"/>
     <n v="4"/>
     <n v="6"/>
-    <n v="28"/>
-    <n v="0.71"/>
+    <x v="2"/>
+    <x v="5"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9062,8 +10477,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="29"/>
-    <n v="0.66"/>
+    <x v="1"/>
+    <x v="6"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9080,8 +10495,8 @@
     <x v="0"/>
     <n v="4"/>
     <n v="6"/>
-    <n v="29"/>
-    <n v="0.67"/>
+    <x v="1"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9098,8 +10513,8 @@
     <x v="0"/>
     <n v="4"/>
     <n v="6"/>
-    <n v="29"/>
-    <n v="0.64"/>
+    <x v="1"/>
+    <x v="7"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9116,8 +10531,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="30"/>
-    <n v="0.67"/>
+    <x v="0"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9134,8 +10549,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="29"/>
-    <n v="0.67"/>
+    <x v="1"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9152,8 +10567,8 @@
     <x v="3"/>
     <n v="5"/>
     <n v="8"/>
-    <n v="29"/>
-    <n v="0.67"/>
+    <x v="1"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9170,8 +10585,8 @@
     <x v="4"/>
     <n v="6"/>
     <n v="9"/>
-    <n v="28"/>
-    <n v="0.68"/>
+    <x v="2"/>
+    <x v="3"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9188,8 +10603,8 @@
     <x v="0"/>
     <n v="4"/>
     <n v="6"/>
-    <n v="28"/>
-    <n v="0.7"/>
+    <x v="2"/>
+    <x v="4"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9206,8 +10621,8 @@
     <x v="0"/>
     <n v="4"/>
     <n v="6"/>
-    <n v="28"/>
-    <n v="0.71"/>
+    <x v="2"/>
+    <x v="5"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9224,8 +10639,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="28"/>
-    <n v="0.71"/>
+    <x v="2"/>
+    <x v="5"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="0"/>
@@ -9242,8 +10657,8 @@
     <x v="5"/>
     <n v="9"/>
     <n v="15"/>
-    <n v="30"/>
-    <n v="0.62"/>
+    <x v="0"/>
+    <x v="8"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9260,8 +10675,8 @@
     <x v="6"/>
     <n v="9"/>
     <n v="13"/>
-    <n v="30"/>
-    <n v="0.62"/>
+    <x v="0"/>
+    <x v="8"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9278,8 +10693,8 @@
     <x v="6"/>
     <n v="9"/>
     <n v="13"/>
-    <n v="30"/>
-    <n v="0.62"/>
+    <x v="0"/>
+    <x v="8"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9296,8 +10711,8 @@
     <x v="7"/>
     <n v="7"/>
     <n v="11"/>
-    <n v="30"/>
-    <n v="0.64"/>
+    <x v="0"/>
+    <x v="7"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9314,8 +10729,8 @@
     <x v="8"/>
     <n v="10"/>
     <n v="16"/>
-    <n v="30"/>
-    <n v="0.62"/>
+    <x v="0"/>
+    <x v="8"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9332,8 +10747,8 @@
     <x v="8"/>
     <n v="10"/>
     <n v="16"/>
-    <n v="29"/>
-    <n v="0.63"/>
+    <x v="1"/>
+    <x v="9"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9350,8 +10765,8 @@
     <x v="8"/>
     <n v="10"/>
     <n v="16"/>
-    <n v="29"/>
-    <n v="0.65"/>
+    <x v="1"/>
+    <x v="1"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9368,8 +10783,8 @@
     <x v="9"/>
     <n v="11"/>
     <n v="17"/>
-    <n v="29"/>
-    <n v="0.67"/>
+    <x v="1"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9386,8 +10801,8 @@
     <x v="10"/>
     <n v="12"/>
     <n v="18"/>
-    <n v="29"/>
-    <n v="0.67"/>
+    <x v="1"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9404,8 +10819,8 @@
     <x v="8"/>
     <n v="10"/>
     <n v="16"/>
-    <n v="29"/>
-    <n v="0.68"/>
+    <x v="1"/>
+    <x v="3"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9422,8 +10837,8 @@
     <x v="8"/>
     <n v="10"/>
     <n v="16"/>
-    <n v="29"/>
-    <n v="0.71"/>
+    <x v="1"/>
+    <x v="5"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9440,8 +10855,8 @@
     <x v="9"/>
     <n v="11"/>
     <n v="17"/>
-    <n v="30"/>
-    <n v="0.69"/>
+    <x v="0"/>
+    <x v="0"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9458,8 +10873,8 @@
     <x v="8"/>
     <n v="10"/>
     <n v="16"/>
-    <n v="29"/>
-    <n v="0.65"/>
+    <x v="1"/>
+    <x v="1"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9476,8 +10891,8 @@
     <x v="6"/>
     <n v="9"/>
     <n v="13"/>
-    <n v="30"/>
-    <n v="0.65"/>
+    <x v="0"/>
+    <x v="1"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9494,8 +10909,8 @@
     <x v="8"/>
     <n v="10"/>
     <n v="16"/>
-    <n v="30"/>
-    <n v="0.63"/>
+    <x v="0"/>
+    <x v="9"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9512,8 +10927,8 @@
     <x v="5"/>
     <n v="9"/>
     <n v="15"/>
-    <n v="32"/>
-    <n v="0.55000000000000004"/>
+    <x v="3"/>
+    <x v="10"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9530,8 +10945,8 @@
     <x v="9"/>
     <n v="11"/>
     <n v="17"/>
-    <n v="32"/>
-    <n v="0.55000000000000004"/>
+    <x v="3"/>
+    <x v="10"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9548,8 +10963,8 @@
     <x v="11"/>
     <n v="8"/>
     <n v="12"/>
-    <n v="32"/>
-    <n v="0.56000000000000005"/>
+    <x v="3"/>
+    <x v="11"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9566,8 +10981,8 @@
     <x v="6"/>
     <n v="9"/>
     <n v="13"/>
-    <n v="31"/>
-    <n v="0.56000000000000005"/>
+    <x v="4"/>
+    <x v="11"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9584,8 +10999,8 @@
     <x v="9"/>
     <n v="11"/>
     <n v="17"/>
-    <n v="30"/>
-    <n v="0.56000000000000005"/>
+    <x v="0"/>
+    <x v="11"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9602,8 +11017,8 @@
     <x v="6"/>
     <n v="9"/>
     <n v="13"/>
-    <n v="31"/>
-    <n v="0.56999999999999995"/>
+    <x v="4"/>
+    <x v="12"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9620,8 +11035,8 @@
     <x v="8"/>
     <n v="10"/>
     <n v="16"/>
-    <n v="30"/>
-    <n v="0.59"/>
+    <x v="0"/>
+    <x v="13"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9638,8 +11053,8 @@
     <x v="12"/>
     <n v="15"/>
     <n v="23"/>
-    <n v="30"/>
-    <n v="0.62"/>
+    <x v="0"/>
+    <x v="8"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9656,8 +11071,8 @@
     <x v="13"/>
     <n v="15"/>
     <n v="24"/>
-    <n v="30"/>
-    <n v="0.64"/>
+    <x v="0"/>
+    <x v="7"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9674,8 +11089,8 @@
     <x v="5"/>
     <n v="9"/>
     <n v="15"/>
-    <n v="30"/>
-    <n v="0.63"/>
+    <x v="0"/>
+    <x v="9"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9692,8 +11107,8 @@
     <x v="11"/>
     <n v="8"/>
     <n v="12"/>
-    <n v="30"/>
-    <n v="0.64"/>
+    <x v="0"/>
+    <x v="7"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9710,8 +11125,8 @@
     <x v="6"/>
     <n v="9"/>
     <n v="13"/>
-    <n v="30"/>
-    <n v="0.65"/>
+    <x v="0"/>
+    <x v="1"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9728,8 +11143,8 @@
     <x v="6"/>
     <n v="9"/>
     <n v="13"/>
-    <n v="30"/>
-    <n v="0.64"/>
+    <x v="0"/>
+    <x v="7"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9746,8 +11161,8 @@
     <x v="9"/>
     <n v="11"/>
     <n v="17"/>
-    <n v="30"/>
-    <n v="0.63"/>
+    <x v="0"/>
+    <x v="9"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9764,8 +11179,8 @@
     <x v="8"/>
     <n v="10"/>
     <n v="16"/>
-    <n v="30"/>
-    <n v="0.65"/>
+    <x v="0"/>
+    <x v="1"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9782,8 +11197,8 @@
     <x v="6"/>
     <n v="9"/>
     <n v="13"/>
-    <n v="30"/>
-    <n v="0.65"/>
+    <x v="0"/>
+    <x v="1"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9800,8 +11215,8 @@
     <x v="8"/>
     <n v="10"/>
     <n v="16"/>
-    <n v="29"/>
-    <n v="0.69"/>
+    <x v="1"/>
+    <x v="0"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9818,8 +11233,8 @@
     <x v="9"/>
     <n v="11"/>
     <n v="17"/>
-    <n v="32"/>
-    <n v="0.66"/>
+    <x v="3"/>
+    <x v="6"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9836,8 +11251,8 @@
     <x v="10"/>
     <n v="12"/>
     <n v="18"/>
-    <n v="30"/>
-    <n v="0.65"/>
+    <x v="0"/>
+    <x v="1"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9854,8 +11269,8 @@
     <x v="13"/>
     <n v="15"/>
     <n v="24"/>
-    <n v="32"/>
-    <n v="0.63"/>
+    <x v="3"/>
+    <x v="9"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9872,8 +11287,8 @@
     <x v="14"/>
     <n v="12"/>
     <n v="19"/>
-    <n v="33"/>
-    <n v="0.52"/>
+    <x v="5"/>
+    <x v="14"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9890,8 +11305,8 @@
     <x v="14"/>
     <n v="12"/>
     <n v="19"/>
-    <n v="35"/>
-    <n v="0.5"/>
+    <x v="6"/>
+    <x v="15"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9908,8 +11323,8 @@
     <x v="15"/>
     <n v="14"/>
     <n v="22"/>
-    <n v="34"/>
-    <n v="0.49"/>
+    <x v="7"/>
+    <x v="16"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9926,8 +11341,8 @@
     <x v="13"/>
     <n v="15"/>
     <n v="24"/>
-    <n v="34"/>
-    <n v="0.49"/>
+    <x v="7"/>
+    <x v="16"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9944,8 +11359,8 @@
     <x v="13"/>
     <n v="15"/>
     <n v="24"/>
-    <n v="34"/>
-    <n v="0.52"/>
+    <x v="7"/>
+    <x v="14"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9962,8 +11377,8 @@
     <x v="16"/>
     <n v="16"/>
     <n v="25"/>
-    <n v="33"/>
-    <n v="0.52"/>
+    <x v="5"/>
+    <x v="14"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9980,8 +11395,8 @@
     <x v="17"/>
     <n v="19"/>
     <n v="29"/>
-    <n v="32"/>
-    <n v="0.54"/>
+    <x v="3"/>
+    <x v="17"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -9998,8 +11413,8 @@
     <x v="18"/>
     <n v="17"/>
     <n v="26"/>
-    <n v="31"/>
-    <n v="0.56000000000000005"/>
+    <x v="4"/>
+    <x v="11"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -10016,8 +11431,8 @@
     <x v="17"/>
     <n v="19"/>
     <n v="29"/>
-    <n v="31"/>
-    <n v="0.56000000000000005"/>
+    <x v="4"/>
+    <x v="11"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -10034,8 +11449,8 @@
     <x v="19"/>
     <n v="13"/>
     <n v="20"/>
-    <n v="27"/>
-    <n v="0.8"/>
+    <x v="8"/>
+    <x v="18"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10052,8 +11467,8 @@
     <x v="15"/>
     <n v="14"/>
     <n v="22"/>
-    <n v="27"/>
-    <n v="0.8"/>
+    <x v="8"/>
+    <x v="18"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10070,8 +11485,8 @@
     <x v="14"/>
     <n v="12"/>
     <n v="20"/>
-    <n v="27"/>
-    <n v="0.8"/>
+    <x v="8"/>
+    <x v="18"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10088,8 +11503,8 @@
     <x v="19"/>
     <n v="13"/>
     <n v="20"/>
-    <n v="27"/>
-    <n v="0.79"/>
+    <x v="8"/>
+    <x v="19"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10106,8 +11521,8 @@
     <x v="15"/>
     <n v="14"/>
     <n v="22"/>
-    <n v="27"/>
-    <n v="0.8"/>
+    <x v="8"/>
+    <x v="18"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10124,8 +11539,8 @@
     <x v="12"/>
     <n v="15"/>
     <n v="23"/>
-    <n v="27"/>
-    <n v="0.8"/>
+    <x v="8"/>
+    <x v="18"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10142,8 +11557,8 @@
     <x v="18"/>
     <n v="17"/>
     <n v="26"/>
-    <n v="27"/>
-    <n v="0.79"/>
+    <x v="8"/>
+    <x v="19"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10160,8 +11575,8 @@
     <x v="20"/>
     <n v="18"/>
     <n v="27"/>
-    <n v="27"/>
-    <n v="0.79"/>
+    <x v="8"/>
+    <x v="19"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10178,8 +11593,8 @@
     <x v="15"/>
     <n v="14"/>
     <n v="22"/>
-    <n v="27"/>
-    <n v="0.76"/>
+    <x v="8"/>
+    <x v="20"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10196,8 +11611,8 @@
     <x v="14"/>
     <n v="12"/>
     <n v="19"/>
-    <n v="27"/>
-    <n v="0.8"/>
+    <x v="8"/>
+    <x v="18"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10214,8 +11629,8 @@
     <x v="0"/>
     <n v="4"/>
     <n v="6"/>
-    <n v="27"/>
-    <n v="0.77"/>
+    <x v="8"/>
+    <x v="21"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10232,8 +11647,8 @@
     <x v="0"/>
     <n v="4"/>
     <n v="6"/>
-    <n v="27"/>
-    <n v="0.73"/>
+    <x v="8"/>
+    <x v="22"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10250,8 +11665,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="27"/>
-    <n v="0.71"/>
+    <x v="8"/>
+    <x v="5"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10268,8 +11683,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="27"/>
-    <n v="0.71"/>
+    <x v="8"/>
+    <x v="5"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10286,8 +11701,8 @@
     <x v="1"/>
     <n v="3"/>
     <n v="5"/>
-    <n v="27"/>
-    <n v="0.69"/>
+    <x v="8"/>
+    <x v="0"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10304,8 +11719,8 @@
     <x v="7"/>
     <n v="7"/>
     <n v="11"/>
-    <n v="27"/>
-    <n v="0.57999999999999996"/>
+    <x v="8"/>
+    <x v="23"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10322,8 +11737,8 @@
     <x v="7"/>
     <n v="7"/>
     <n v="11"/>
-    <n v="27"/>
-    <n v="0.56000000000000005"/>
+    <x v="8"/>
+    <x v="11"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10340,8 +11755,8 @@
     <x v="7"/>
     <n v="7"/>
     <n v="11"/>
-    <n v="27"/>
-    <n v="0.54"/>
+    <x v="8"/>
+    <x v="17"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10358,8 +11773,8 @@
     <x v="10"/>
     <n v="12"/>
     <n v="18"/>
-    <n v="29"/>
-    <n v="0.73"/>
+    <x v="1"/>
+    <x v="22"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="2"/>
@@ -10376,8 +11791,8 @@
     <x v="5"/>
     <n v="9"/>
     <n v="15"/>
-    <n v="33"/>
-    <n v="0.56999999999999995"/>
+    <x v="5"/>
+    <x v="12"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -10394,8 +11809,8 @@
     <x v="7"/>
     <n v="7"/>
     <n v="11"/>
-    <n v="32"/>
-    <n v="0.56999999999999995"/>
+    <x v="3"/>
+    <x v="12"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -10412,8 +11827,8 @@
     <x v="7"/>
     <n v="7"/>
     <n v="11"/>
-    <n v="31"/>
-    <n v="0.61"/>
+    <x v="4"/>
+    <x v="24"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -10430,8 +11845,8 @@
     <x v="7"/>
     <n v="7"/>
     <n v="11"/>
-    <n v="31"/>
-    <n v="0.65"/>
+    <x v="4"/>
+    <x v="1"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -10448,8 +11863,8 @@
     <x v="7"/>
     <n v="7"/>
     <n v="11"/>
-    <n v="30"/>
-    <n v="0.66"/>
+    <x v="0"/>
+    <x v="6"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -10466,8 +11881,8 @@
     <x v="6"/>
     <n v="9"/>
     <n v="13"/>
-    <n v="30"/>
-    <n v="0.67"/>
+    <x v="0"/>
+    <x v="2"/>
     <n v="0.16"/>
     <n v="0.3"/>
     <x v="1"/>
@@ -10476,7 +11891,168 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37ED737D-3F36-E24F-9BD7-02891A5A600F}" name="樞紐分析表4" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCD5E50B-9C4D-044C-93EE-4E867E2C8A75}" name="樞紐分析表5" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:C11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="16">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item h="1" x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField numFmtId="178" showAll="0"/>
+    <pivotField dataField="1" numFmtId="178" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="9" showAll="0">
+      <items count="26">
+        <item x="16"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="17"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="13"/>
+        <item x="24"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="22"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField numFmtId="177" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="15" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="平均值 - Humidity" fld="12" subtotal="average" baseField="0" baseItem="0" numFmtId="179"/>
+    <dataField name="平均值 - Temperature" fld="11" subtotal="average" baseField="0" baseItem="0" numFmtId="180"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37ED737D-3F36-E24F-9BD7-02891A5A600F}" name="樞紐分析表4" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B114:D122" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField showAll="0"/>
@@ -10678,8 +12254,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{720ED964-7BC8-684A-BBAE-C23D41EA4814}" name="樞紐分析表3" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{720ED964-7BC8-684A-BBAE-C23D41EA4814}" name="樞紐分析表3" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="B77:E82" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -10906,8 +12482,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6D587E1-3F11-8949-B3A1-51B0FE88E26C}" name="樞紐分析表2" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6D587E1-3F11-8949-B3A1-51B0FE88E26C}" name="樞紐分析表2" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="B46:G51" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -11253,8 +12829,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55D91BA8-991E-C349-8944-9ABD03A461D9}" name="樞紐分析表1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55D91BA8-991E-C349-8944-9ABD03A461D9}" name="樞紐分析表1" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="B7:E13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -11675,6 +13251,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F5D92A3-9EFE-4F49-A19D-AA0F67C9A577}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="9">
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="C4" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.65499999999999992</v>
+      </c>
+      <c r="C5" s="10">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="C6" s="10">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0.60727272727272741</v>
+      </c>
+      <c r="C7" s="10">
+        <v>30.545454545454547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0.57400000000000007</v>
+      </c>
+      <c r="C8" s="10">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0.5257142857142858</v>
+      </c>
+      <c r="C9" s="10">
+        <v>32.714285714285715</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0.62166666666666659</v>
+      </c>
+      <c r="C10" s="10">
+        <v>31.166666666666668</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="9">
+        <v>0.60999999999999976</v>
+      </c>
+      <c r="C11" s="10">
+        <v>30.76</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F155B05C-8FBC-5D47-8E46-498532CDE74B}">
   <dimension ref="A1:P94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -16337,7 +18037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B281C63B-8C58-9F41-8F1B-004B6747AE34}">
   <dimension ref="B5:G132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
